--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AE26EB-0D99-44DB-888A-9B9F691F2387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48B647F-C623-43F4-85AD-1DA7DD761B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B9A1C2-23A2-4F24-BCEE-35EFDEE6F899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B03E67E-E33A-471D-9056-E65FEAD8BF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1598,15 +1598,6 @@
     <t>TBD+K93</t>
   </si>
   <si>
-    <t>How many countries have airports in this dataset?</t>
-  </si>
-  <si>
-    <t>Combien de pays possèdent des aéroports dans ce jeu de données ?</t>
-  </si>
-  <si>
-    <t>كم عدد الدول التي تحتوي على مطارات في هذه المجموعة من البيانات؟</t>
-  </si>
-  <si>
     <t>How many students are members of Department3?</t>
   </si>
   <si>
@@ -1632,6 +1623,15 @@
   </si>
   <si>
     <t>Lecturer3@Department0.University0.edu</t>
+  </si>
+  <si>
+    <t>Which country has the highest average airport elevation?</t>
+  </si>
+  <si>
+    <t>Quel pays a l'élévation moyenne des aéroports la plus haute?"</t>
+  </si>
+  <si>
+    <t>أي دولة لديها أعلى متوسط ارتفاع للمطارات في هذه المجموعة من البيانات?</t>
   </si>
 </sst>
 </file>
@@ -1777,8 +1777,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1824,13 +1822,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2147,12 +2147,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="26" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2365,3065 +2365,3065 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
     </row>
     <row r="2" spans="1:14" s="7" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="16">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18" t="s">
+      <c r="F2" s="16"/>
+      <c r="G2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="14"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>1</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="15"/>
+      <c r="L3" s="13"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="15"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <v>1</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="15"/>
+      <c r="L5" s="13"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <v>1</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20" t="s">
+      <c r="F6" s="18"/>
+      <c r="G6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="15"/>
+      <c r="L6" s="13"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>1</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="15"/>
+      <c r="L7" s="13"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>1</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20" t="s">
+      <c r="F8" s="18"/>
+      <c r="G8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="15"/>
+      <c r="L8" s="13"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <v>1</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20" t="s">
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="15"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="18">
         <v>1</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20" t="s">
+      <c r="F10" s="18"/>
+      <c r="G10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="K10" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="15"/>
+      <c r="L10" s="13"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="20">
         <v>1</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="16"/>
+      <c r="L11" s="14"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="18">
         <v>1</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20" t="s">
+      <c r="F12" s="18"/>
+      <c r="G12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="K12" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="15"/>
+      <c r="L12" s="13"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="18">
         <v>1</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20" t="s">
+      <c r="F13" s="18"/>
+      <c r="G13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="L13" s="15"/>
+      <c r="L13" s="13"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="18">
         <v>1</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20" t="s">
+      <c r="F14" s="18"/>
+      <c r="G14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="L14" s="15"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="18">
         <v>1</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20" t="s">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="J15" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K15" s="21" t="s">
+      <c r="K15" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="L15" s="15"/>
+      <c r="L15" s="13"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="18">
         <v>1</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20" t="s">
+      <c r="F16" s="18"/>
+      <c r="G16" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="K16" s="21" t="s">
+      <c r="K16" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="L16" s="15"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="18">
         <v>1</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20" t="s">
+      <c r="F17" s="18"/>
+      <c r="G17" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="K17" s="21" t="s">
+      <c r="K17" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="L17" s="15"/>
+      <c r="L17" s="13"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="18">
         <v>1</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20" t="s">
+      <c r="F18" s="18"/>
+      <c r="G18" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="21" t="s">
+      <c r="I18" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="K18" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="L18" s="15"/>
+      <c r="L18" s="13"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
     <row r="19" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="18">
         <v>1</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20" t="s">
+      <c r="F19" s="18"/>
+      <c r="G19" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="J19" s="21" t="s">
+      <c r="J19" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="K19" s="21" t="s">
+      <c r="K19" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="L19" s="15"/>
+      <c r="L19" s="13"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
     <row r="20" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="20">
         <v>1</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="K20" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="L20" s="16"/>
+      <c r="L20" s="14"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
     <row r="21" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="20">
         <v>1</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="20"/>
+      <c r="G21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="L21" s="16"/>
+      <c r="L21" s="14"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
     <row r="22" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="20">
         <v>1</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22" t="s">
+      <c r="F22" s="20"/>
+      <c r="G22" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="J22" s="23" t="s">
+      <c r="J22" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="L22" s="16"/>
+      <c r="L22" s="14"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
     <row r="23" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="20">
         <v>1</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22" t="s">
+      <c r="F23" s="20"/>
+      <c r="G23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="I23" s="23" t="s">
+      <c r="I23" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K23" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="L23" s="16"/>
+      <c r="L23" s="14"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
     <row r="24" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="20">
         <v>1</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="20"/>
+      <c r="G24" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="J24" s="23" t="s">
+      <c r="J24" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="L24" s="16"/>
+      <c r="L24" s="14"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
     <row r="25" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="18">
         <v>1</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20" t="s">
+      <c r="F25" s="18"/>
+      <c r="G25" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I25" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="J25" s="21" t="s">
+      <c r="J25" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="K25" s="21" t="s">
+      <c r="K25" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="L25" s="15"/>
+      <c r="L25" s="13"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
     <row r="26" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20" t="s">
+      <c r="F26" s="18"/>
+      <c r="G26" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="I26" s="21" t="s">
+      <c r="I26" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="J26" s="21" t="s">
+      <c r="J26" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="K26" s="21" t="s">
+      <c r="K26" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="L26" s="15"/>
+      <c r="L26" s="13"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
     <row r="27" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="18">
         <v>1</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20" t="s">
+      <c r="F27" s="18"/>
+      <c r="G27" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="I27" s="21" t="s">
+      <c r="I27" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="J27" s="21" t="s">
+      <c r="J27" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="21" t="s">
+      <c r="K27" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="L27" s="15"/>
+      <c r="L27" s="13"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
     <row r="28" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="18">
         <v>1</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20" t="s">
+      <c r="F28" s="18"/>
+      <c r="G28" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H28" s="21" t="s">
+      <c r="H28" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="I28" s="21" t="s">
+      <c r="I28" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="J28" s="21" t="s">
+      <c r="J28" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="K28" s="21" t="s">
+      <c r="K28" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="L28" s="15"/>
+      <c r="L28" s="13"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
     <row r="29" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="18">
         <v>1</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20" t="s">
+      <c r="F29" s="18"/>
+      <c r="G29" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="J29" s="21" t="s">
+      <c r="J29" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="K29" s="21" t="s">
+      <c r="K29" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="L29" s="15"/>
+      <c r="L29" s="13"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
     <row r="30" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="18">
         <v>1</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="18"/>
+      <c r="G30" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="J30" s="21" t="s">
+      <c r="J30" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="K30" s="21" t="s">
+      <c r="K30" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="L30" s="15"/>
+      <c r="L30" s="13"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
     <row r="31" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="18">
         <v>1</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20" t="s">
+      <c r="F31" s="18"/>
+      <c r="G31" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="I31" s="21" t="s">
+      <c r="I31" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="J31" s="21" t="s">
+      <c r="J31" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="K31" s="21" t="s">
+      <c r="K31" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="L31" s="15"/>
+      <c r="L31" s="13"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
     <row r="32" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="18">
         <v>1</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20" t="s">
+      <c r="F32" s="18"/>
+      <c r="G32" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="I32" s="21" t="s">
+      <c r="I32" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J32" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="K32" s="21" t="s">
+      <c r="K32" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="L32" s="15"/>
+      <c r="L32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
     <row r="33" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="18">
         <v>1</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20" t="s">
+      <c r="F33" s="18"/>
+      <c r="G33" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H33" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="I33" s="21" t="s">
+      <c r="I33" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="J33" s="21" t="s">
+      <c r="J33" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="K33" s="21" t="s">
+      <c r="K33" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="L33" s="15"/>
+      <c r="L33" s="13"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
     <row r="34" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="18">
         <v>1</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20" t="s">
+      <c r="F34" s="18"/>
+      <c r="G34" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="I34" s="21" t="s">
+      <c r="I34" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="J34" s="21" t="s">
+      <c r="J34" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="K34" s="21" t="s">
+      <c r="K34" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="L34" s="15"/>
+      <c r="L34" s="13"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
     <row r="35" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="18">
         <v>1</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20" t="s">
+      <c r="F35" s="18"/>
+      <c r="G35" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H35" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="I35" s="21" t="s">
+      <c r="I35" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="J35" s="21" t="s">
+      <c r="J35" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="K35" s="21" t="s">
+      <c r="K35" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="L35" s="15"/>
+      <c r="L35" s="13"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
     <row r="36" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="18">
         <v>1</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20" t="s">
+      <c r="F36" s="18"/>
+      <c r="G36" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="I36" s="21" t="s">
+      <c r="I36" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="J36" s="21" t="s">
+      <c r="J36" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="K36" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="L36" s="15"/>
+      <c r="L36" s="13"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
     <row r="37" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="18">
         <v>1</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20" t="s">
+      <c r="F37" s="18"/>
+      <c r="G37" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H37" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="K37" s="21">
+      <c r="K37" s="19">
         <v>4</v>
       </c>
-      <c r="L37" s="15"/>
+      <c r="L37" s="13"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
     <row r="38" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="18">
         <v>1</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20" t="s">
+      <c r="F38" s="18"/>
+      <c r="G38" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H38" s="21" t="s">
+      <c r="H38" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="J38" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="19">
         <v>6</v>
       </c>
-      <c r="L38" s="15"/>
+      <c r="L38" s="13"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
     <row r="39" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="18">
         <v>1</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20" t="s">
+      <c r="F39" s="18"/>
+      <c r="G39" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H39" s="21" t="s">
+      <c r="H39" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="I39" s="21" t="s">
+      <c r="I39" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="J39" s="21" t="s">
+      <c r="J39" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="K39" s="21" t="s">
+      <c r="K39" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="L39" s="15"/>
+      <c r="L39" s="13"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
     <row r="40" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="20" t="s">
+      <c r="A40" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="18">
         <v>1</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20" t="s">
+      <c r="F40" s="18"/>
+      <c r="G40" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H40" s="21" t="s">
+      <c r="H40" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="I40" s="21" t="s">
+      <c r="I40" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="J40" s="21" t="s">
+      <c r="J40" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="K40" s="21" t="s">
+      <c r="K40" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="L40" s="15"/>
+      <c r="L40" s="13"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
     <row r="41" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="18">
         <v>1</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20" t="s">
+      <c r="F41" s="18"/>
+      <c r="G41" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H41" s="21" t="s">
+      <c r="H41" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I41" s="21" t="s">
+      <c r="I41" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="J41" s="21" t="s">
+      <c r="J41" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="K41" s="21" t="s">
+      <c r="K41" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="L41" s="15"/>
+      <c r="L41" s="13"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
     <row r="42" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
+      <c r="A42" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="18">
         <v>2</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H42" s="21" t="s">
+      <c r="H42" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="I42" s="21" t="s">
+      <c r="I42" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="J42" s="21" t="s">
+      <c r="J42" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="K42" s="21">
+      <c r="K42" s="19">
         <v>45</v>
       </c>
-      <c r="L42" s="15"/>
+      <c r="L42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
     <row r="43" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="18">
         <v>2</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H43" s="21" t="s">
+      <c r="H43" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="I43" s="21" t="s">
+      <c r="I43" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="J43" s="21" t="s">
+      <c r="J43" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="K43" s="21">
+      <c r="K43" s="19">
         <v>61</v>
       </c>
-      <c r="L43" s="15"/>
+      <c r="L43" s="13"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
     <row r="44" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="18">
         <v>2</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G44" s="20" t="s">
+      <c r="G44" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="21" t="s">
+      <c r="H44" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="I44" s="21" t="s">
+      <c r="I44" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="J44" s="21" t="s">
+      <c r="J44" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="K44" s="21">
+      <c r="K44" s="19">
         <v>57</v>
       </c>
-      <c r="L44" s="15"/>
+      <c r="L44" s="13"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
     <row r="45" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="18">
         <v>2</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="G45" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H45" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="I45" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="J45" s="21" t="s">
+      <c r="J45" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="K45" s="21">
+      <c r="K45" s="19">
         <v>3</v>
       </c>
-      <c r="L45" s="15"/>
+      <c r="L45" s="13"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
     <row r="46" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="18">
         <v>2</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="G46" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H46" s="21" t="s">
+      <c r="H46" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="I46" s="21" t="s">
+      <c r="I46" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="J46" s="21" t="s">
+      <c r="J46" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="K46" s="21">
+      <c r="K46" s="19">
         <v>2</v>
       </c>
-      <c r="L46" s="15"/>
+      <c r="L46" s="13"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
     </row>
     <row r="47" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="18">
         <v>2</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="G47" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H47" s="21" t="s">
+      <c r="H47" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="I47" s="21" t="s">
+      <c r="I47" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="J47" s="21" t="s">
+      <c r="J47" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="K47" s="21">
+      <c r="K47" s="19">
         <v>41</v>
       </c>
-      <c r="L47" s="15"/>
+      <c r="L47" s="13"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
     </row>
     <row r="48" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="18">
         <v>2</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="G48" s="20" t="s">
+      <c r="G48" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H48" s="21" t="s">
+      <c r="H48" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="I48" s="21" t="s">
+      <c r="I48" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="J48" s="21" t="s">
+      <c r="J48" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="K48" s="21" t="s">
+      <c r="K48" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="L48" s="15"/>
+      <c r="L48" s="13"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
     </row>
     <row r="49" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="20" t="s">
+      <c r="A49" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="18">
         <v>2</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="G49" s="20" t="s">
+      <c r="G49" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H49" s="21" t="s">
+      <c r="H49" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="I49" s="21" t="s">
+      <c r="I49" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="J49" s="21" t="s">
+      <c r="J49" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="K49" s="21" t="s">
+      <c r="K49" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="L49" s="15"/>
+      <c r="L49" s="13"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
     </row>
     <row r="50" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="18">
         <v>2</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="F50" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="G50" s="20" t="s">
+      <c r="G50" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H50" s="21" t="s">
+      <c r="H50" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="I50" s="21" t="s">
+      <c r="I50" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="J50" s="21" t="s">
+      <c r="J50" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="K50" s="21" t="s">
+      <c r="K50" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="L50" s="15"/>
+      <c r="L50" s="13"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
     </row>
     <row r="51" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="18">
         <v>2</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="F51" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="G51" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H51" s="21" t="s">
+      <c r="H51" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="I51" s="21" t="s">
+      <c r="I51" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="J51" s="21" t="s">
+      <c r="J51" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K51" s="21" t="s">
+      <c r="K51" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="L51" s="15"/>
+      <c r="L51" s="13"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
     </row>
     <row r="52" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="18">
         <v>2</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="G52" s="20" t="s">
+      <c r="G52" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H52" s="21" t="s">
+      <c r="H52" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="I52" s="21" t="s">
+      <c r="I52" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="J52" s="21" t="s">
+      <c r="J52" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="K52" s="21" t="s">
+      <c r="K52" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="L52" s="15"/>
+      <c r="L52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
     </row>
     <row r="53" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="18">
         <v>2</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="F53" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="G53" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="I53" s="21" t="s">
+      <c r="I53" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="J53" s="21" t="s">
+      <c r="J53" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="K53" s="21" t="s">
+      <c r="K53" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="L53" s="15"/>
+      <c r="L53" s="13"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
     </row>
     <row r="54" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="s">
+      <c r="A54" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="18">
         <v>2</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="G54" s="20" t="s">
+      <c r="G54" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H54" s="21" t="s">
+      <c r="H54" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="I54" s="21" t="s">
+      <c r="I54" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="J54" s="21" t="s">
+      <c r="J54" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="K54" s="21" t="s">
+      <c r="K54" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="L54" s="15"/>
+      <c r="L54" s="13"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
     </row>
     <row r="55" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="18">
         <v>2</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F55" s="20" t="s">
+      <c r="F55" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="G55" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H55" s="21" t="s">
+      <c r="H55" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="I55" s="21" t="s">
+      <c r="I55" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="J55" s="21" t="s">
+      <c r="J55" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="K55" s="21" t="s">
+      <c r="K55" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="L55" s="15"/>
+      <c r="L55" s="13"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
     </row>
     <row r="56" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="18">
         <v>2</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="F56" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="G56" s="20" t="s">
+      <c r="G56" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H56" s="21" t="s">
+      <c r="H56" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I56" s="21" t="s">
+      <c r="I56" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="J56" s="21" t="s">
+      <c r="J56" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="K56" s="21" t="s">
+      <c r="K56" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="L56" s="15"/>
+      <c r="L56" s="13"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
     </row>
     <row r="57" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="18">
         <v>2</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="F57" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="G57" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H57" s="21" t="s">
+      <c r="H57" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="I57" s="21" t="s">
+      <c r="I57" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="J57" s="21" t="s">
+      <c r="J57" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="K57" s="21" t="s">
+      <c r="K57" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="L57" s="15"/>
+      <c r="L57" s="13"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
     </row>
     <row r="58" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="18">
         <v>2</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="G58" s="20" t="s">
+      <c r="G58" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H58" s="21" t="s">
+      <c r="H58" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="I58" s="21" t="s">
+      <c r="I58" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="J58" s="21" t="s">
+      <c r="J58" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="K58" s="21" t="s">
+      <c r="K58" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="L58" s="15"/>
+      <c r="L58" s="13"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
     </row>
     <row r="59" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="18">
         <v>2</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="D59" s="20" t="s">
+      <c r="D59" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="F59" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="G59" s="20" t="s">
+      <c r="G59" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H59" s="21" t="s">
+      <c r="H59" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="I59" s="21" t="s">
+      <c r="I59" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="J59" s="21" t="s">
+      <c r="J59" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="K59" s="21" t="s">
+      <c r="K59" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="L59" s="15"/>
+      <c r="L59" s="13"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="18">
         <v>2</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D60" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="F60" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="G60" s="20" t="s">
+      <c r="G60" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H60" s="21" t="s">
+      <c r="H60" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="I60" s="21" t="s">
+      <c r="I60" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="J60" s="21" t="s">
+      <c r="J60" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="K60" s="21" t="s">
+      <c r="K60" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="L60" s="15"/>
+      <c r="L60" s="13"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
     </row>
     <row r="61" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
+      <c r="A61" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="18">
         <v>2</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="F61" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="G61" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H61" s="21" t="s">
+      <c r="H61" s="19" t="s">
         <v>310</v>
       </c>
-      <c r="I61" s="21" t="s">
+      <c r="I61" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="J61" s="21" t="s">
+      <c r="J61" s="19" t="s">
         <v>312</v>
       </c>
-      <c r="K61" s="21" t="s">
+      <c r="K61" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="L61" s="15"/>
+      <c r="L61" s="13"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
     </row>
     <row r="62" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="18">
         <v>2</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="F62" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="G62" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H62" s="21" t="s">
+      <c r="H62" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="I62" s="21" t="s">
+      <c r="I62" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="J62" s="21" t="s">
+      <c r="J62" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="K62" s="21" t="s">
+      <c r="K62" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="L62" s="15"/>
+      <c r="L62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
     </row>
     <row r="63" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="18">
         <v>2</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F63" s="20" t="s">
+      <c r="F63" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="G63" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H63" s="21" t="s">
+      <c r="H63" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="I63" s="21" t="s">
+      <c r="I63" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="J63" s="21" t="s">
+      <c r="J63" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="K63" s="21" t="s">
+      <c r="K63" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="L63" s="15"/>
+      <c r="L63" s="13"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
     </row>
     <row r="64" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="18">
         <v>2</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="F64" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="G64" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H64" s="21" t="s">
+      <c r="H64" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="I64" s="21" t="s">
+      <c r="I64" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="J64" s="21" t="s">
+      <c r="J64" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="K64" s="21" t="s">
+      <c r="K64" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="L64" s="15"/>
+      <c r="L64" s="13"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
     </row>
     <row r="65" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="18">
         <v>3</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20" t="s">
+      <c r="F65" s="18"/>
+      <c r="G65" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H65" s="21" t="s">
+      <c r="H65" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="I65" s="21" t="s">
+      <c r="I65" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="J65" s="21" t="s">
+      <c r="J65" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="K65" s="21"/>
-      <c r="L65" s="15"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="13"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
     </row>
     <row r="66" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="18">
         <v>3</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D66" s="20" t="s">
+      <c r="D66" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20" t="s">
+      <c r="F66" s="18"/>
+      <c r="G66" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H66" s="21" t="s">
+      <c r="H66" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="I66" s="21" t="s">
+      <c r="I66" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="J66" s="21" t="s">
+      <c r="J66" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="K66" s="21"/>
-      <c r="L66" s="15"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="13"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
     </row>
     <row r="67" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="18">
         <v>3</v>
       </c>
-      <c r="C67" s="20" t="s">
+      <c r="C67" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="20" t="s">
+      <c r="D67" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="E67" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20" t="s">
+      <c r="F67" s="18"/>
+      <c r="G67" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H67" s="21" t="s">
+      <c r="H67" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="I67" s="21" t="s">
+      <c r="I67" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="J67" s="21" t="s">
+      <c r="J67" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="K67" s="21"/>
-      <c r="L67" s="15"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="13"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
     </row>
     <row r="68" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="B68" s="20">
+      <c r="B68" s="18">
         <v>3</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D68" s="20" t="s">
+      <c r="D68" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20" t="s">
+      <c r="F68" s="18"/>
+      <c r="G68" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H68" s="21" t="s">
+      <c r="H68" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="I68" s="21" t="s">
+      <c r="I68" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="J68" s="21" t="s">
+      <c r="J68" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="K68" s="21" t="s">
+      <c r="K68" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="L68" s="15"/>
+      <c r="L68" s="13"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
     </row>
     <row r="69" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="B69" s="20">
+      <c r="B69" s="18">
         <v>3</v>
       </c>
-      <c r="C69" s="20" t="s">
+      <c r="C69" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D69" s="20" t="s">
+      <c r="D69" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20" t="s">
+      <c r="F69" s="18"/>
+      <c r="G69" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H69" s="21" t="s">
+      <c r="H69" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="I69" s="21" t="s">
+      <c r="I69" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="J69" s="21" t="s">
+      <c r="J69" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="K69" s="21" t="s">
+      <c r="K69" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="L69" s="15"/>
+      <c r="L69" s="13"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
     </row>
     <row r="70" spans="1:14" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="B70" s="20">
+      <c r="B70" s="18">
         <v>3</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D70" s="20" t="s">
+      <c r="D70" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E70" s="20" t="s">
+      <c r="E70" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20" t="s">
+      <c r="F70" s="18"/>
+      <c r="G70" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H70" s="21" t="s">
+      <c r="H70" s="19" t="s">
         <v>356</v>
       </c>
-      <c r="I70" s="21" t="s">
+      <c r="I70" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="J70" s="21" t="s">
+      <c r="J70" s="19" t="s">
         <v>358</v>
       </c>
-      <c r="K70" s="21" t="s">
+      <c r="K70" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="L70" s="15"/>
+      <c r="L70" s="13"/>
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
     </row>
     <row r="71" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="B71" s="20">
+      <c r="B71" s="18">
         <v>3</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D71" s="20" t="s">
+      <c r="D71" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E71" s="20" t="s">
+      <c r="E71" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20" t="s">
+      <c r="F71" s="18"/>
+      <c r="G71" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H71" s="21" t="s">
+      <c r="H71" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="I71" s="21" t="s">
+      <c r="I71" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="J71" s="21" t="s">
+      <c r="J71" s="19" t="s">
         <v>363</v>
       </c>
-      <c r="K71" s="21" t="s">
+      <c r="K71" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="L71" s="15"/>
+      <c r="L71" s="13"/>
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
     </row>
     <row r="72" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="B72" s="20">
+      <c r="B72" s="18">
         <v>3</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="D72" s="20" t="s">
+      <c r="D72" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20" t="s">
+      <c r="F72" s="18"/>
+      <c r="G72" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H72" s="21" t="s">
+      <c r="H72" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="I72" s="21" t="s">
+      <c r="I72" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="J72" s="21" t="s">
+      <c r="J72" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="K72" s="21" t="s">
+      <c r="K72" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="L72" s="15"/>
+      <c r="L72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
     </row>
     <row r="73" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="B73" s="20">
+      <c r="B73" s="18">
         <v>3</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="D73" s="20" t="s">
+      <c r="D73" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20" t="s">
+      <c r="F73" s="18"/>
+      <c r="G73" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H73" s="21" t="s">
+      <c r="H73" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="I73" s="21" t="s">
+      <c r="I73" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="J73" s="21" t="s">
+      <c r="J73" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="K73" s="21" t="s">
+      <c r="K73" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="L73" s="15"/>
+      <c r="L73" s="13"/>
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="18">
         <v>3</v>
       </c>
-      <c r="C74" s="20" t="s">
+      <c r="C74" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="D74" s="20" t="s">
+      <c r="D74" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E74" s="20" t="s">
+      <c r="E74" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20" t="s">
+      <c r="F74" s="18"/>
+      <c r="G74" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H74" s="21" t="s">
+      <c r="H74" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="I74" s="21" t="s">
+      <c r="I74" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="J74" s="21" t="s">
+      <c r="J74" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K74" s="21" t="s">
+      <c r="K74" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="L74" s="15"/>
+      <c r="L74" s="13"/>
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="B75" s="20">
+      <c r="B75" s="18">
         <v>3</v>
       </c>
-      <c r="C75" s="20" t="s">
+      <c r="C75" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="D75" s="20" t="s">
+      <c r="D75" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E75" s="20" t="s">
+      <c r="E75" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20" t="s">
+      <c r="F75" s="18"/>
+      <c r="G75" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H75" s="21" t="s">
+      <c r="H75" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="I75" s="21" t="s">
+      <c r="I75" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="J75" s="21" t="s">
+      <c r="J75" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="K75" s="21" t="s">
+      <c r="K75" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="L75" s="15"/>
+      <c r="L75" s="13"/>
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="B76" s="20">
+      <c r="B76" s="18">
         <v>3</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="D76" s="20" t="s">
+      <c r="D76" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E76" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20" t="s">
+      <c r="F76" s="18"/>
+      <c r="G76" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H76" s="21" t="s">
+      <c r="H76" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="I76" s="21" t="s">
+      <c r="I76" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="J76" s="21" t="s">
+      <c r="J76" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="K76" s="21" t="s">
+      <c r="K76" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="L76" s="15"/>
+      <c r="L76" s="13"/>
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="18">
         <v>3</v>
       </c>
-      <c r="C77" s="20" t="s">
+      <c r="C77" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="D77" s="20" t="s">
+      <c r="D77" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E77" s="20" t="s">
+      <c r="E77" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20" t="s">
+      <c r="F77" s="18"/>
+      <c r="G77" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H77" s="21" t="s">
+      <c r="H77" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="I77" s="21" t="s">
+      <c r="I77" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="J77" s="21" t="s">
+      <c r="J77" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="K77" s="21" t="s">
+      <c r="K77" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="L77" s="15"/>
+      <c r="L77" s="13"/>
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="20" t="s">
+      <c r="A78" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="18">
         <v>3</v>
       </c>
-      <c r="C78" s="20" t="s">
+      <c r="C78" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="D78" s="20" t="s">
+      <c r="D78" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E78" s="20" t="s">
+      <c r="E78" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20" t="s">
+      <c r="F78" s="18"/>
+      <c r="G78" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H78" s="21" t="s">
+      <c r="H78" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="I78" s="21" t="s">
+      <c r="I78" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="J78" s="21" t="s">
+      <c r="J78" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="K78" s="21" t="s">
+      <c r="K78" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L78" s="15"/>
+      <c r="L78" s="13"/>
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="20" t="s">
+      <c r="A79" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="B79" s="20">
+      <c r="B79" s="18">
         <v>3</v>
       </c>
-      <c r="C79" s="20" t="s">
+      <c r="C79" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="D79" s="20" t="s">
+      <c r="D79" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E79" s="20" t="s">
+      <c r="E79" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20" t="s">
+      <c r="F79" s="18"/>
+      <c r="G79" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H79" s="21" t="s">
+      <c r="H79" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="I79" s="21" t="s">
+      <c r="I79" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="J79" s="21" t="s">
+      <c r="J79" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="K79" s="24" t="s">
+      <c r="K79" s="22" t="s">
         <v>400</v>
       </c>
-      <c r="L79" s="15"/>
+      <c r="L79" s="13"/>
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="B80" s="20">
+      <c r="B80" s="18">
         <v>3</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="D80" s="20" t="s">
+      <c r="D80" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E80" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20" t="s">
+      <c r="F80" s="18"/>
+      <c r="G80" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H80" s="21" t="s">
+      <c r="H80" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="I80" s="21" t="s">
+      <c r="I80" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="J80" s="21" t="s">
+      <c r="J80" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="K80" s="21" t="s">
+      <c r="K80" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="L80" s="15"/>
+      <c r="L80" s="13"/>
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="B81" s="20">
+      <c r="B81" s="18">
         <v>3</v>
       </c>
-      <c r="C81" s="20" t="s">
+      <c r="C81" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="D81" s="20" t="s">
+      <c r="D81" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E81" s="20" t="s">
+      <c r="E81" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20" t="s">
+      <c r="F81" s="18"/>
+      <c r="G81" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H81" s="21" t="s">
+      <c r="H81" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="I81" s="21" t="s">
+      <c r="I81" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="J81" s="21" t="s">
+      <c r="J81" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="K81" s="24" t="s">
+      <c r="K81" s="22" t="s">
         <v>405</v>
       </c>
-      <c r="L81" s="15"/>
+      <c r="L81" s="13"/>
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="B82" s="20">
+      <c r="B82" s="18">
         <v>3</v>
       </c>
-      <c r="C82" s="20" t="s">
+      <c r="C82" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="D82" s="20" t="s">
+      <c r="D82" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E82" s="20" t="s">
+      <c r="E82" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20" t="s">
+      <c r="F82" s="18"/>
+      <c r="G82" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H82" s="21" t="s">
+      <c r="H82" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="I82" s="21" t="s">
+      <c r="I82" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="J82" s="21" t="s">
+      <c r="J82" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="K82" s="24" t="s">
+      <c r="K82" s="22" t="s">
         <v>405</v>
       </c>
-      <c r="L82" s="15"/>
+      <c r="L82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
     </row>
     <row r="83" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="25" t="s">
+      <c r="A83" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="B83" s="25">
+      <c r="B83" s="23">
         <v>1</v>
       </c>
-      <c r="C83" s="25" t="s">
+      <c r="C83" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="25" t="s">
+      <c r="D83" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="25" t="s">
+      <c r="E83" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25" t="s">
+      <c r="F83" s="23"/>
+      <c r="G83" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H83" s="26" t="s">
+      <c r="H83" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="I83" s="26" t="s">
+      <c r="I83" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="J83" s="26" t="s">
+      <c r="J83" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="K83" s="26" t="s">
-        <v>530</v>
+      <c r="K83" s="24" t="s">
+        <v>527</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
     </row>
     <row r="84" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="25" t="s">
+      <c r="A84" s="23" t="s">
         <v>419</v>
       </c>
-      <c r="B84" s="25">
+      <c r="B84" s="23">
         <v>1</v>
       </c>
-      <c r="C84" s="25" t="s">
+      <c r="C84" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="25" t="s">
+      <c r="D84" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E84" s="25" t="s">
+      <c r="E84" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25" t="s">
+      <c r="F84" s="23"/>
+      <c r="G84" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H84" s="26" t="s">
+      <c r="H84" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="I84" s="26" t="s">
+      <c r="I84" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="J84" s="26" t="s">
+      <c r="J84" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="K84" s="26" t="s">
+      <c r="K84" s="24" t="s">
         <v>515</v>
       </c>
       <c r="L84" s="5"/>
@@ -5431,35 +5431,35 @@
       <c r="N84" s="5"/>
     </row>
     <row r="85" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A85" s="25" t="s">
+      <c r="A85" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="B85" s="25">
+      <c r="B85" s="23">
         <v>1</v>
       </c>
-      <c r="C85" s="25" t="s">
+      <c r="C85" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D85" s="25" t="s">
+      <c r="D85" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E85" s="25" t="s">
+      <c r="E85" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25" t="s">
+      <c r="F85" s="23"/>
+      <c r="G85" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H85" s="26" t="s">
+      <c r="H85" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="I85" s="26" t="s">
+      <c r="I85" s="24" t="s">
         <v>425</v>
       </c>
-      <c r="J85" s="26" t="s">
+      <c r="J85" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="K85" s="26" t="s">
+      <c r="K85" s="24" t="s">
         <v>516</v>
       </c>
       <c r="L85" s="5"/>
@@ -5467,71 +5467,71 @@
       <c r="N85" s="5"/>
     </row>
     <row r="86" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="25" t="s">
+      <c r="A86" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="B86" s="25">
+      <c r="B86" s="23">
         <v>1</v>
       </c>
-      <c r="C86" s="25" t="s">
+      <c r="C86" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D86" s="25" t="s">
+      <c r="D86" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E86" s="25" t="s">
+      <c r="E86" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25" t="s">
+      <c r="F86" s="23"/>
+      <c r="G86" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H86" s="26" t="s">
+      <c r="H86" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="I86" s="26" t="s">
+      <c r="I86" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="J86" s="26" t="s">
+      <c r="J86" s="24" t="s">
         <v>430</v>
       </c>
-      <c r="K86" s="26" t="s">
-        <v>531</v>
+      <c r="K86" s="24" t="s">
+        <v>528</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
     </row>
     <row r="87" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A87" s="25" t="s">
+      <c r="A87" s="23" t="s">
         <v>431</v>
       </c>
-      <c r="B87" s="25">
+      <c r="B87" s="23">
         <v>1</v>
       </c>
-      <c r="C87" s="25" t="s">
+      <c r="C87" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D87" s="25" t="s">
+      <c r="D87" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E87" s="25" t="s">
+      <c r="E87" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25" t="s">
+      <c r="F87" s="23"/>
+      <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="26" t="s">
+      <c r="H87" s="24" t="s">
         <v>432</v>
       </c>
-      <c r="I87" s="26" t="s">
+      <c r="I87" s="24" t="s">
         <v>433</v>
       </c>
-      <c r="J87" s="26" t="s">
+      <c r="J87" s="24" t="s">
         <v>434</v>
       </c>
-      <c r="K87" s="26" t="s">
+      <c r="K87" s="24" t="s">
         <v>418</v>
       </c>
       <c r="L87" s="5"/>
@@ -5539,35 +5539,35 @@
       <c r="N87" s="5"/>
     </row>
     <row r="88" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="25" t="s">
+      <c r="A88" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="B88" s="25">
+      <c r="B88" s="23">
         <v>1</v>
       </c>
-      <c r="C88" s="25" t="s">
+      <c r="C88" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D88" s="25" t="s">
+      <c r="D88" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E88" s="25" t="s">
+      <c r="E88" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25" t="s">
+      <c r="F88" s="23"/>
+      <c r="G88" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H88" s="26" t="s">
+      <c r="H88" s="24" t="s">
         <v>436</v>
       </c>
-      <c r="I88" s="26" t="s">
+      <c r="I88" s="24" t="s">
         <v>437</v>
       </c>
-      <c r="J88" s="26" t="s">
+      <c r="J88" s="24" t="s">
         <v>438</v>
       </c>
-      <c r="K88" s="26" t="s">
+      <c r="K88" s="24" t="s">
         <v>517</v>
       </c>
       <c r="L88" s="5"/>
@@ -5575,35 +5575,35 @@
       <c r="N88" s="5"/>
     </row>
     <row r="89" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="25" t="s">
+      <c r="A89" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="B89" s="25">
+      <c r="B89" s="23">
         <v>1</v>
       </c>
-      <c r="C89" s="25" t="s">
+      <c r="C89" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D89" s="25" t="s">
+      <c r="D89" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E89" s="25" t="s">
+      <c r="E89" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25" t="s">
+      <c r="F89" s="23"/>
+      <c r="G89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H89" s="26" t="s">
+      <c r="H89" s="24" t="s">
         <v>440</v>
       </c>
-      <c r="I89" s="26" t="s">
+      <c r="I89" s="24" t="s">
         <v>441</v>
       </c>
-      <c r="J89" s="26" t="s">
+      <c r="J89" s="24" t="s">
         <v>442</v>
       </c>
-      <c r="K89" s="26" t="s">
+      <c r="K89" s="24" t="s">
         <v>93</v>
       </c>
       <c r="L89" s="5"/>
@@ -5611,35 +5611,35 @@
       <c r="N89" s="5"/>
     </row>
     <row r="90" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
+      <c r="A90" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="B90" s="25">
+      <c r="B90" s="23">
         <v>1</v>
       </c>
-      <c r="C90" s="25" t="s">
+      <c r="C90" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="25" t="s">
+      <c r="D90" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E90" s="25" t="s">
+      <c r="E90" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25" t="s">
+      <c r="F90" s="23"/>
+      <c r="G90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H90" s="26" t="s">
+      <c r="H90" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="I90" s="26" t="s">
+      <c r="I90" s="24" t="s">
         <v>445</v>
       </c>
-      <c r="J90" s="26" t="s">
+      <c r="J90" s="24" t="s">
         <v>446</v>
       </c>
-      <c r="K90" s="26" t="s">
+      <c r="K90" s="24" t="s">
         <v>520</v>
       </c>
       <c r="L90" s="5"/>
@@ -5647,35 +5647,35 @@
       <c r="N90" s="5"/>
     </row>
     <row r="91" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A91" s="25" t="s">
+      <c r="A91" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="B91" s="25">
+      <c r="B91" s="23">
         <v>1</v>
       </c>
-      <c r="C91" s="25" t="s">
+      <c r="C91" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D91" s="25" t="s">
+      <c r="D91" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E91" s="25" t="s">
+      <c r="E91" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25" t="s">
+      <c r="F91" s="23"/>
+      <c r="G91" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H91" s="26" t="s">
+      <c r="H91" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="I91" s="26" t="s">
+      <c r="I91" s="24" t="s">
         <v>521</v>
       </c>
-      <c r="J91" s="26" t="s">
+      <c r="J91" s="24" t="s">
         <v>449</v>
       </c>
-      <c r="K91" s="26" t="s">
+      <c r="K91" s="24" t="s">
         <v>522</v>
       </c>
       <c r="L91" s="5"/>
@@ -5683,71 +5683,71 @@
       <c r="N91" s="5"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="25" t="s">
+      <c r="A92" s="23" t="s">
         <v>450</v>
       </c>
-      <c r="B92" s="25">
+      <c r="B92" s="23">
         <v>1</v>
       </c>
-      <c r="C92" s="25" t="s">
+      <c r="C92" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D92" s="25" t="s">
+      <c r="D92" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E92" s="25" t="s">
+      <c r="E92" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25" t="s">
+      <c r="F92" s="23"/>
+      <c r="G92" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H92" s="26" t="s">
+      <c r="H92" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>530</v>
+      </c>
+      <c r="J92" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="K92" s="25" t="s">
         <v>532</v>
-      </c>
-      <c r="I92" s="26" t="s">
-        <v>533</v>
-      </c>
-      <c r="J92" s="26" t="s">
-        <v>534</v>
-      </c>
-      <c r="K92" s="27" t="s">
-        <v>535</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
     </row>
     <row r="93" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="23" t="s">
         <v>451</v>
       </c>
-      <c r="B93" s="25">
+      <c r="B93" s="23">
         <v>1</v>
       </c>
-      <c r="C93" s="25" t="s">
+      <c r="C93" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D93" s="25" t="s">
+      <c r="D93" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E93" s="25" t="s">
+      <c r="E93" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25" t="s">
+      <c r="F93" s="23"/>
+      <c r="G93" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H93" s="24" t="s">
         <v>513</v>
       </c>
-      <c r="I93" s="26" t="s">
+      <c r="I93" s="24" t="s">
         <v>452</v>
       </c>
-      <c r="J93" s="26" t="s">
+      <c r="J93" s="24" t="s">
         <v>453</v>
       </c>
-      <c r="K93" s="26" t="s">
+      <c r="K93" s="24" t="s">
         <v>523</v>
       </c>
       <c r="L93" s="5"/>
@@ -5755,35 +5755,35 @@
       <c r="N93" s="5"/>
     </row>
     <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="23" t="s">
         <v>454</v>
       </c>
-      <c r="B94" s="25">
+      <c r="B94" s="23">
         <v>1</v>
       </c>
-      <c r="C94" s="25" t="s">
+      <c r="C94" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D94" s="25" t="s">
+      <c r="D94" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="E94" s="25" t="s">
+      <c r="E94" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25" t="s">
+      <c r="F94" s="23"/>
+      <c r="G94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H94" s="26" t="s">
+      <c r="H94" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="I94" s="26" t="s">
+      <c r="I94" s="24" t="s">
         <v>456</v>
       </c>
-      <c r="J94" s="26" t="s">
+      <c r="J94" s="24" t="s">
         <v>457</v>
       </c>
-      <c r="K94" s="26" t="s">
+      <c r="K94" s="24" t="s">
         <v>132</v>
       </c>
       <c r="L94" s="5"/>
@@ -5791,35 +5791,35 @@
       <c r="N94" s="5"/>
     </row>
     <row r="95" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="23" t="s">
         <v>458</v>
       </c>
-      <c r="B95" s="25">
+      <c r="B95" s="23">
         <v>1</v>
       </c>
-      <c r="C95" s="25" t="s">
+      <c r="C95" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D95" s="25" t="s">
+      <c r="D95" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="E95" s="25" t="s">
+      <c r="E95" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="F95" s="25"/>
-      <c r="G95" s="25" t="s">
+      <c r="F95" s="23"/>
+      <c r="G95" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H95" s="26" t="s">
+      <c r="H95" s="24" t="s">
         <v>459</v>
       </c>
-      <c r="I95" s="26" t="s">
+      <c r="I95" s="24" t="s">
         <v>460</v>
       </c>
-      <c r="J95" s="26" t="s">
+      <c r="J95" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="K95" s="26" t="s">
+      <c r="K95" s="24" t="s">
         <v>418</v>
       </c>
       <c r="L95" s="5"/>
@@ -5827,35 +5827,35 @@
       <c r="N95" s="5"/>
     </row>
     <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="23" t="s">
         <v>462</v>
       </c>
-      <c r="B96" s="25">
+      <c r="B96" s="23">
         <v>1</v>
       </c>
-      <c r="C96" s="25" t="s">
+      <c r="C96" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D96" s="25" t="s">
+      <c r="D96" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="E96" s="25" t="s">
+      <c r="E96" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25" t="s">
+      <c r="F96" s="23"/>
+      <c r="G96" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H96" s="26" t="s">
+      <c r="H96" s="24" t="s">
         <v>463</v>
       </c>
-      <c r="I96" s="26" t="s">
+      <c r="I96" s="24" t="s">
         <v>464</v>
       </c>
-      <c r="J96" s="26" t="s">
+      <c r="J96" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="K96" s="26" t="s">
+      <c r="K96" s="24" t="s">
         <v>418</v>
       </c>
       <c r="L96" s="5"/>
@@ -5863,37 +5863,37 @@
       <c r="N96" s="5"/>
     </row>
     <row r="97" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="25" t="s">
+      <c r="A97" s="23" t="s">
         <v>466</v>
       </c>
-      <c r="B97" s="25">
+      <c r="B97" s="23">
         <v>2</v>
       </c>
-      <c r="C97" s="25" t="s">
+      <c r="C97" s="23" t="s">
         <v>467</v>
       </c>
-      <c r="D97" s="25" t="s">
+      <c r="D97" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E97" s="25" t="s">
+      <c r="E97" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F97" s="23" t="s">
         <v>467</v>
       </c>
-      <c r="G97" s="25" t="s">
+      <c r="G97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H97" s="26" t="s">
-        <v>524</v>
-      </c>
-      <c r="I97" s="26" t="s">
-        <v>525</v>
-      </c>
-      <c r="J97" s="26" t="s">
-        <v>526</v>
-      </c>
-      <c r="K97" s="26">
+      <c r="H97" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="I97" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="J97" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="K97" s="24">
         <v>30</v>
       </c>
       <c r="L97" s="5"/>
@@ -5901,37 +5901,37 @@
       <c r="N97" s="5"/>
     </row>
     <row r="98" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
+      <c r="A98" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="B98" s="25">
+      <c r="B98" s="23">
         <v>2</v>
       </c>
-      <c r="C98" s="25" t="s">
+      <c r="C98" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D98" s="25" t="s">
+      <c r="D98" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E98" s="25" t="s">
+      <c r="E98" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F98" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="G98" s="25" t="s">
+      <c r="G98" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H98" s="26" t="s">
-        <v>527</v>
-      </c>
-      <c r="I98" s="26" t="s">
-        <v>528</v>
-      </c>
-      <c r="J98" s="26" t="s">
-        <v>529</v>
-      </c>
-      <c r="K98" s="26">
+      <c r="H98" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="I98" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="J98" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="K98" s="24">
         <v>120</v>
       </c>
       <c r="L98" s="5"/>
@@ -5939,37 +5939,37 @@
       <c r="N98" s="5"/>
     </row>
     <row r="99" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A99" s="25" t="s">
+      <c r="A99" s="23" t="s">
         <v>469</v>
       </c>
-      <c r="B99" s="25">
+      <c r="B99" s="23">
         <v>2</v>
       </c>
-      <c r="C99" s="25" t="s">
+      <c r="C99" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="D99" s="25" t="s">
+      <c r="D99" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E99" s="25" t="s">
+      <c r="E99" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F99" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="G99" s="25" t="s">
+      <c r="G99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H99" s="26" t="s">
+      <c r="H99" s="24" t="s">
         <v>470</v>
       </c>
-      <c r="I99" s="26" t="s">
+      <c r="I99" s="24" t="s">
         <v>471</v>
       </c>
-      <c r="J99" s="26" t="s">
+      <c r="J99" s="24" t="s">
         <v>472</v>
       </c>
-      <c r="K99" s="26" t="s">
+      <c r="K99" s="24" t="s">
         <v>518</v>
       </c>
       <c r="L99" s="5"/>
@@ -5977,35 +5977,35 @@
       <c r="N99" s="5"/>
     </row>
     <row r="100" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="25" t="s">
+      <c r="A100" s="23" t="s">
         <v>473</v>
       </c>
-      <c r="B100" s="25">
+      <c r="B100" s="23">
         <v>3</v>
       </c>
-      <c r="C100" s="25" t="s">
+      <c r="C100" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="D100" s="25" t="s">
+      <c r="D100" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="E100" s="25" t="s">
+      <c r="E100" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="F100" s="25"/>
-      <c r="G100" s="25" t="s">
+      <c r="F100" s="23"/>
+      <c r="G100" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="H100" s="26" t="s">
+      <c r="H100" s="24" t="s">
         <v>514</v>
       </c>
-      <c r="I100" s="26" t="s">
+      <c r="I100" s="24" t="s">
         <v>474</v>
       </c>
-      <c r="J100" s="26" t="s">
+      <c r="J100" s="24" t="s">
         <v>475</v>
       </c>
-      <c r="K100" s="26" t="s">
+      <c r="K100" s="24" t="s">
         <v>519</v>
       </c>
       <c r="L100" s="5"/>
@@ -6013,35 +6013,35 @@
       <c r="N100" s="5"/>
     </row>
     <row r="101" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A101" s="25" t="s">
+      <c r="A101" s="23" t="s">
         <v>476</v>
       </c>
-      <c r="B101" s="25">
+      <c r="B101" s="23">
         <v>1</v>
       </c>
-      <c r="C101" s="25" t="s">
+      <c r="C101" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="D101" s="25" t="s">
+      <c r="D101" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="E101" s="25" t="s">
+      <c r="E101" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25" t="s">
+      <c r="F101" s="23"/>
+      <c r="G101" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H101" s="26" t="s">
+      <c r="H101" s="24" t="s">
         <v>477</v>
       </c>
-      <c r="I101" s="26" t="s">
+      <c r="I101" s="24" t="s">
         <v>478</v>
       </c>
-      <c r="J101" s="26" t="s">
+      <c r="J101" s="24" t="s">
         <v>479</v>
       </c>
-      <c r="K101" s="26">
+      <c r="K101" s="24">
         <v>58</v>
       </c>
       <c r="L101" s="5"/>
@@ -6049,18 +6049,18 @@
       <c r="N101" s="5"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H102" s="10"/>
-      <c r="I102" s="10"/>
-      <c r="J102" s="10"/>
-      <c r="K102" s="10"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H103" s="10"/>
-      <c r="I103" s="10"/>
-      <c r="K103" s="10"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="K103" s="8"/>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B03E67E-E33A-471D-9056-E65FEAD8BF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A96AFDA-C445-4B33-8F3B-BBAA03636370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,43 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Questions!$A$1:$L$73</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6073,7 +6108,10 @@
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
+      <c r="N105" s="5" cm="1">
+        <f t="array" aca="1" ref="N105" ca="1">A83:N105</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="L106" s="5"/>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A96AFDA-C445-4B33-8F3B-BBAA03636370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917F01C6-BDC2-4942-A235-BD42955E414B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1624,9 +1624,6 @@
     <t xml:space="preserve">Course0, GraduateCourse0, GraduateCourse1	</t>
   </si>
   <si>
-    <t>GraduateStudent5 poursuit un diplôme avanc+K90++I91:K91</t>
-  </si>
-  <si>
     <t>University579</t>
   </si>
   <si>
@@ -1667,6 +1664,9 @@
   </si>
   <si>
     <t>أي دولة لديها أعلى متوسط ارتفاع للمطارات في هذه المجموعة من البيانات?</t>
+  </si>
+  <si>
+    <t>GraduateStudent5 poursuit un diplôme avancé — de quelle université a-t-il obtenu son diplôme de licence avant de commencer son master ici ?</t>
   </si>
 </sst>
 </file>
@@ -5423,7 +5423,7 @@
         <v>417</v>
       </c>
       <c r="K83" s="24" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
@@ -5531,7 +5531,7 @@
         <v>430</v>
       </c>
       <c r="K86" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
@@ -5705,13 +5705,13 @@
         <v>448</v>
       </c>
       <c r="I91" s="24" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="J91" s="24" t="s">
         <v>449</v>
       </c>
       <c r="K91" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
@@ -5738,16 +5738,16 @@
         <v>14</v>
       </c>
       <c r="H92" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="I92" s="24" t="s">
         <v>529</v>
       </c>
-      <c r="I92" s="24" t="s">
+      <c r="J92" s="24" t="s">
         <v>530</v>
       </c>
-      <c r="J92" s="24" t="s">
+      <c r="K92" s="25" t="s">
         <v>531</v>
-      </c>
-      <c r="K92" s="25" t="s">
-        <v>532</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
@@ -5783,7 +5783,7 @@
         <v>453</v>
       </c>
       <c r="K93" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="5"/>
@@ -5920,13 +5920,13 @@
         <v>14</v>
       </c>
       <c r="H97" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="I97" s="24" t="s">
         <v>533</v>
       </c>
-      <c r="I97" s="24" t="s">
+      <c r="J97" s="24" t="s">
         <v>534</v>
-      </c>
-      <c r="J97" s="24" t="s">
-        <v>535</v>
       </c>
       <c r="K97" s="24">
         <v>30</v>
@@ -5958,13 +5958,13 @@
         <v>14</v>
       </c>
       <c r="H98" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="I98" s="24" t="s">
         <v>524</v>
       </c>
-      <c r="I98" s="24" t="s">
+      <c r="J98" s="24" t="s">
         <v>525</v>
-      </c>
-      <c r="J98" s="24" t="s">
-        <v>526</v>
       </c>
       <c r="K98" s="24">
         <v>120</v>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917F01C6-BDC2-4942-A235-BD42955E414B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240C2497-80AD-42B2-9AC7-C4E64DAE9DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="534">
   <si>
     <t>id</t>
   </si>
@@ -1315,9 +1315,6 @@
     <t>بالنسبة لرحلة الخطوط الجوية النمساوية OS295 بين فيينا وبوخارست، ما هي بوابة المغادرة المخصصة؟</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>single_kg1_011</t>
   </si>
   <si>
@@ -1417,12 +1414,6 @@
     <t>single_kg3_008</t>
   </si>
   <si>
-    <t>Quel est le nom officiel et complet de Department2 tel qu'enregistré dans ce graphe de connaissances?</t>
-  </si>
-  <si>
-    <t>ما هو الاسم الرسمي الكامل لـ Department2 كما هو مسجل في هذا الرسم البياني المعرفي؟</t>
-  </si>
-  <si>
     <t>cross_kg_013</t>
   </si>
   <si>
@@ -1606,30 +1597,18 @@
     <t>Is the runway surface at FRA made of ASP?</t>
   </si>
   <si>
-    <t>397, 246, 344, 426, 448</t>
-  </si>
-  <si>
-    <t>2048, 1664, 640, 1088</t>
-  </si>
-  <si>
     <t>Munich</t>
   </si>
   <si>
     <t>ESB</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t xml:space="preserve">Course0, GraduateCourse0, GraduateCourse1	</t>
   </si>
   <si>
     <t>University579</t>
   </si>
   <si>
-    <t>TBD+K93</t>
-  </si>
-  <si>
     <t>How many students are members of Department3?</t>
   </si>
   <si>
@@ -1667,6 +1646,21 @@
   </si>
   <si>
     <t>GraduateStudent5 poursuit un diplôme avancé — de quelle université a-t-il obtenu son diplôme de licence avant de commencer son master ici ?</t>
+  </si>
+  <si>
+    <t>Bulgaria, 1742.00</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>www.University0.edu</t>
+  </si>
+  <si>
+    <t>De quelle université fait partie Department2 ?</t>
+  </si>
+  <si>
+    <t>ما هي الجامعة التي ينتمي إليها Department2؟</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1709,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1752,6 +1746,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1797,7 +1797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1863,9 +1863,17 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2182,12 +2190,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="A1" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2195,32 +2203,32 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2229,7 +2237,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B9" s="2"/>
     </row>
@@ -2238,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2246,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2254,7 +2262,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2262,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2270,7 +2278,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2278,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2286,15 +2294,15 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2302,15 +2310,15 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2319,32 +2327,32 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2353,24 +2361,24 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -5423,7 +5431,7 @@
         <v>417</v>
       </c>
       <c r="K83" s="24" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
@@ -5431,7 +5439,7 @@
     </row>
     <row r="84" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B84" s="23">
         <v>1</v>
@@ -5450,16 +5458,16 @@
         <v>14</v>
       </c>
       <c r="H84" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="I84" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="I84" s="24" t="s">
+      <c r="J84" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="J84" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="K84" s="24" t="s">
-        <v>515</v>
+      <c r="K84" s="24">
+        <v>397</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
@@ -5467,7 +5475,7 @@
     </row>
     <row r="85" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="23" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B85" s="23">
         <v>1</v>
@@ -5486,16 +5494,16 @@
         <v>14</v>
       </c>
       <c r="H85" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="I85" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="I85" s="24" t="s">
+      <c r="J85" s="24" t="s">
         <v>425</v>
       </c>
-      <c r="J85" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="K85" s="24" t="s">
-        <v>516</v>
+      <c r="K85" s="24">
+        <v>2048</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
@@ -5503,7 +5511,7 @@
     </row>
     <row r="86" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B86" s="23">
         <v>1</v>
@@ -5522,16 +5530,16 @@
         <v>14</v>
       </c>
       <c r="H86" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="I86" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="I86" s="24" t="s">
+      <c r="J86" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="J86" s="24" t="s">
-        <v>430</v>
-      </c>
       <c r="K86" s="24" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
@@ -5539,7 +5547,7 @@
     </row>
     <row r="87" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B87" s="23">
         <v>1</v>
@@ -5558,16 +5566,16 @@
         <v>14</v>
       </c>
       <c r="H87" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="I87" s="24" t="s">
         <v>432</v>
       </c>
-      <c r="I87" s="24" t="s">
+      <c r="J87" s="24" t="s">
         <v>433</v>
       </c>
-      <c r="J87" s="24" t="s">
-        <v>434</v>
-      </c>
-      <c r="K87" s="24" t="s">
-        <v>418</v>
+      <c r="K87" s="24">
+        <v>13123</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
@@ -5575,7 +5583,7 @@
     </row>
     <row r="88" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B88" s="23">
         <v>1</v>
@@ -5594,16 +5602,16 @@
         <v>14</v>
       </c>
       <c r="H88" s="24" t="s">
+        <v>435</v>
+      </c>
+      <c r="I88" s="24" t="s">
         <v>436</v>
       </c>
-      <c r="I88" s="24" t="s">
+      <c r="J88" s="24" t="s">
         <v>437</v>
       </c>
-      <c r="J88" s="24" t="s">
-        <v>438</v>
-      </c>
       <c r="K88" s="24" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
@@ -5611,7 +5619,7 @@
     </row>
     <row r="89" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B89" s="23">
         <v>1</v>
@@ -5630,13 +5638,13 @@
         <v>14</v>
       </c>
       <c r="H89" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I89" s="24" t="s">
         <v>440</v>
       </c>
-      <c r="I89" s="24" t="s">
+      <c r="J89" s="24" t="s">
         <v>441</v>
-      </c>
-      <c r="J89" s="24" t="s">
-        <v>442</v>
       </c>
       <c r="K89" s="24" t="s">
         <v>93</v>
@@ -5647,7 +5655,7 @@
     </row>
     <row r="90" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="23" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B90" s="23">
         <v>1</v>
@@ -5666,16 +5674,16 @@
         <v>14</v>
       </c>
       <c r="H90" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="I90" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="I90" s="24" t="s">
+      <c r="J90" s="24" t="s">
         <v>445</v>
       </c>
-      <c r="J90" s="24" t="s">
-        <v>446</v>
-      </c>
       <c r="K90" s="24" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
@@ -5683,7 +5691,7 @@
     </row>
     <row r="91" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B91" s="23">
         <v>1</v>
@@ -5702,24 +5710,24 @@
         <v>14</v>
       </c>
       <c r="H91" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="I91" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="J91" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="I91" s="24" t="s">
-        <v>535</v>
-      </c>
-      <c r="J91" s="24" t="s">
-        <v>449</v>
-      </c>
       <c r="K91" s="24" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="28"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="23" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B92" s="23">
         <v>1</v>
@@ -5738,24 +5746,24 @@
         <v>14</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="J92" s="24" t="s">
-        <v>530</v>
-      </c>
-      <c r="K92" s="25" t="s">
-        <v>531</v>
-      </c>
-      <c r="L92" s="5"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-    </row>
-    <row r="93" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+      <c r="K92" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="L92" s="27"/>
+      <c r="M92" s="28"/>
+      <c r="N92" s="28"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B93" s="23">
         <v>1</v>
@@ -5774,24 +5782,24 @@
         <v>14</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I93" s="24" t="s">
-        <v>452</v>
+        <v>532</v>
       </c>
       <c r="J93" s="24" t="s">
-        <v>453</v>
-      </c>
-      <c r="K93" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="L93" s="5"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
+        <v>533</v>
+      </c>
+      <c r="K93" s="29" t="s">
+        <v>531</v>
+      </c>
+      <c r="L93" s="27"/>
+      <c r="M93" s="28"/>
+      <c r="N93" s="28"/>
     </row>
     <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="23" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B94" s="23">
         <v>1</v>
@@ -5810,13 +5818,13 @@
         <v>14</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I94" s="24" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J94" s="24" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K94" s="24" t="s">
         <v>132</v>
@@ -5827,7 +5835,7 @@
     </row>
     <row r="95" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="23" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B95" s="23">
         <v>1</v>
@@ -5846,16 +5854,16 @@
         <v>14</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I95" s="24" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J95" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="K95" s="24" t="s">
-        <v>418</v>
+        <v>458</v>
+      </c>
+      <c r="K95" s="24">
+        <v>325</v>
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
@@ -5863,7 +5871,7 @@
     </row>
     <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="23" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B96" s="23">
         <v>1</v>
@@ -5882,16 +5890,16 @@
         <v>14</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J96" s="24" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="K96" s="24" t="s">
-        <v>418</v>
+        <v>93</v>
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
@@ -5899,13 +5907,13 @@
     </row>
     <row r="97" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="23" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B97" s="23">
         <v>2</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D97" s="23" t="s">
         <v>59</v>
@@ -5914,22 +5922,22 @@
         <v>214</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G97" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="I97" s="24" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="J97" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="K97" s="24">
-        <v>30</v>
+        <v>527</v>
+      </c>
+      <c r="K97" s="24" t="s">
+        <v>529</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
@@ -5937,7 +5945,7 @@
     </row>
     <row r="98" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="23" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B98" s="23">
         <v>2</v>
@@ -5958,13 +5966,13 @@
         <v>14</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="J98" s="24" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="K98" s="24">
         <v>120</v>
@@ -5975,7 +5983,7 @@
     </row>
     <row r="99" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="23" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B99" s="23">
         <v>2</v>
@@ -5996,16 +6004,16 @@
         <v>14</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I99" s="24" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J99" s="24" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="K99" s="24" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
@@ -6013,7 +6021,7 @@
     </row>
     <row r="100" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="23" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B100" s="23">
         <v>3</v>
@@ -6032,16 +6040,16 @@
         <v>128</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I100" s="24" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J100" s="24" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="K100" s="24" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
@@ -6049,7 +6057,7 @@
     </row>
     <row r="101" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B101" s="23">
         <v>1</v>
@@ -6068,13 +6076,13 @@
         <v>14</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I101" s="24" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J101" s="24" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="K101" s="24">
         <v>58</v>
@@ -6160,6 +6168,7 @@
     <hyperlink ref="K72" r:id="rId2" display="www.University0.edu" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="K73" r:id="rId3" display="www.University0.edu" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="K92" r:id="rId4" xr:uid="{F402B207-9C31-4349-83A1-BCC6F56AEDB2}"/>
+    <hyperlink ref="K93" r:id="rId5" xr:uid="{68DBCBB5-52F3-45C1-8520-C539E611CD0B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240C2497-80AD-42B2-9AC7-C4E64DAE9DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5566393A-4232-43DA-81F1-C8278FC5C8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1609,15 +1609,6 @@
     <t>University579</t>
   </si>
   <si>
-    <t>How many students are members of Department3?</t>
-  </si>
-  <si>
-    <t>Combien d'étudiants sont membres du Department3 ?</t>
-  </si>
-  <si>
-    <t>كم عدد الطلاب الأعضاء في Department3؟</t>
-  </si>
-  <si>
     <t>C18</t>
   </si>
   <si>
@@ -1654,13 +1645,22 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>www.University0.edu</t>
-  </si>
-  <si>
     <t>De quelle université fait partie Department2 ?</t>
   </si>
   <si>
     <t>ما هي الجامعة التي ينتمي إليها Department2؟</t>
+  </si>
+  <si>
+    <t>"['www.University0.edu']"</t>
+  </si>
+  <si>
+    <t>How many members are in Department3?</t>
+  </si>
+  <si>
+    <t>Combien de membres compte le Department3 ?</t>
+  </si>
+  <si>
+    <t>كم عدد الأعضاء في Department3؟</t>
   </si>
 </sst>
 </file>
@@ -1863,8 +1863,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1874,6 +1872,8 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2190,12 +2190,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>477</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -5431,7 +5431,7 @@
         <v>417</v>
       </c>
       <c r="K83" s="24" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
@@ -5539,7 +5539,7 @@
         <v>429</v>
       </c>
       <c r="K86" s="24" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
@@ -5713,7 +5713,7 @@
         <v>447</v>
       </c>
       <c r="I91" s="24" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J91" s="24" t="s">
         <v>448</v>
@@ -5722,8 +5722,8 @@
         <v>515</v>
       </c>
       <c r="L91" s="5"/>
-      <c r="M91" s="28"/>
-      <c r="N91" s="28"/>
+      <c r="M91" s="26"/>
+      <c r="N91" s="26"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="23" t="s">
@@ -5746,20 +5746,20 @@
         <v>14</v>
       </c>
       <c r="H92" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="J92" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="K92" s="27" t="s">
         <v>521</v>
       </c>
-      <c r="I92" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="J92" s="24" t="s">
-        <v>523</v>
-      </c>
-      <c r="K92" s="29" t="s">
-        <v>524</v>
-      </c>
-      <c r="L92" s="27"/>
-      <c r="M92" s="28"/>
-      <c r="N92" s="28"/>
+      <c r="L92" s="25"/>
+      <c r="M92" s="26"/>
+      <c r="N92" s="26"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="23" t="s">
@@ -5785,17 +5785,17 @@
         <v>510</v>
       </c>
       <c r="I93" s="24" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J93" s="24" t="s">
-        <v>533</v>
-      </c>
-      <c r="K93" s="29" t="s">
-        <v>531</v>
-      </c>
-      <c r="L93" s="27"/>
-      <c r="M93" s="28"/>
-      <c r="N93" s="28"/>
+        <v>529</v>
+      </c>
+      <c r="K93" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="L93" s="25"/>
+      <c r="M93" s="26"/>
+      <c r="N93" s="26"/>
     </row>
     <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="23" t="s">
@@ -5928,22 +5928,22 @@
         <v>14</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="I97" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="J97" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="K97" s="24" t="s">
         <v>526</v>
-      </c>
-      <c r="J97" s="24" t="s">
-        <v>527</v>
-      </c>
-      <c r="K97" s="24" t="s">
-        <v>529</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
       <c r="N97" s="5"/>
     </row>
-    <row r="98" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="23" t="s">
         <v>465</v>
       </c>
@@ -5966,13 +5966,13 @@
         <v>14</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="J98" s="24" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="K98" s="24">
         <v>120</v>
@@ -6049,7 +6049,7 @@
         <v>472</v>
       </c>
       <c r="K100" s="24" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
@@ -6168,9 +6168,9 @@
     <hyperlink ref="K72" r:id="rId2" display="www.University0.edu" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="K73" r:id="rId3" display="www.University0.edu" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="K92" r:id="rId4" xr:uid="{F402B207-9C31-4349-83A1-BCC6F56AEDB2}"/>
-    <hyperlink ref="K93" r:id="rId5" xr:uid="{68DBCBB5-52F3-45C1-8520-C539E611CD0B}"/>
+    <hyperlink ref="K93" r:id="rId5" display="www.University0.edu" xr:uid="{68DBCBB5-52F3-45C1-8520-C539E611CD0B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5566393A-4232-43DA-81F1-C8278FC5C8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F28320-D23C-49EC-BDBF-7B5756C8BBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -904,9 +904,6 @@
     <t>أظهر جميع المطارات الكبيرة.</t>
   </si>
   <si>
-    <t>ARN, AYT, BCN, BEG, BER, BKK, BLQ, BOM, BRI, BRU, CDG, CGN, CHQ, CPH, CTA, DUS, EBL, ESB, FCO, FRA, GRZ, GYD, HAJ, HAM, HEL, IST, JFK, KGS, KRK, LCA, LEJ, LGW, LHR, LUX, MLA, MRS, MUC, NAP, NRT, ORY, OTP, PFO, PMI, PMO, RIX, RMF, SAW, SBZ, SOF, STR, TIA, VCE, VIE, WAW, ZAG, ZRH</t>
-  </si>
-  <si>
     <t>filter_string_kg2_003</t>
   </si>
   <si>
@@ -1372,9 +1369,6 @@
     <t>À des fins d'urbanisme, dans quelle municipalité l'aéroport de Munich est-il officiellement situé?</t>
   </si>
   <si>
-    <t>لأغراض التخطيط الحضري، في أي بلدية يقع مطار ميونخ رسميًا؟</t>
-  </si>
-  <si>
     <t>single_kg2_012</t>
   </si>
   <si>
@@ -1420,9 +1414,6 @@
     <t>Flight OS295 is scheduled to land soon — once you determine its destination airport, what country is that airport officially located in?</t>
   </si>
   <si>
-    <t>Le vol OS295 doit bientôt atterrir — une fois l'aéroport de destination déterminé, dans quel pays cet aéroport se trouve-t-il officiellement?</t>
-  </si>
-  <si>
     <t>من المقرر أن تهبط الرحلة OS295 قريبًا — بعد تحديد مطار الوصول، في أي دولة يقع هذا المطار رسميًا؟</t>
   </si>
   <si>
@@ -1651,9 +1642,6 @@
     <t>ما هي الجامعة التي ينتمي إليها Department2؟</t>
   </si>
   <si>
-    <t>"['www.University0.edu']"</t>
-  </si>
-  <si>
     <t>How many members are in Department3?</t>
   </si>
   <si>
@@ -1661,6 +1649,73 @@
   </si>
   <si>
     <t>كم عدد الأعضاء في Department3؟</t>
+  </si>
+  <si>
+    <t>www.University0.edu</t>
+  </si>
+  <si>
+    <t>ما هي البلدية التي يقع فيها مطار ميونخ رسميًا؟</t>
+  </si>
+  <si>
+    <t>Le vol OS295 doit bientôt atterrir dans un aéroport — quel est le pays où se trouve officiellement cet aéroport?</t>
+  </si>
+  <si>
+    <t>Antalya International Airport
+Bari Karol Wojtyła International Airport
+Belgrade Nikola Tesla Airport
+Berlin Brandenburg Airport
+Bologna Guglielmo Marconi Airport
+Brussels Airport
+Bucharest Henri Coandă International Airport
+Catania-Fontanarossa Airport
+Chania International Airport
+Charles de Gaulle International Airport
+Chhatrapati Shivaji Maharaj International Airport
+Cologne Bonn Airport
+Copenhagen Kastrup Airport
+Düsseldorf Airport
+Erbil International Airport
+Esenboğa International Airport
+Falcone–Borsellino Airport
+Frankfurt Main Airport
+Graz Airport
+Hamburg Helmut Schmidt Airport
+Hannover Airport
+Helsinki Vantaa Airport
+Heydar Aliyev International Airport
+Istanbul Sabiha Gökçen International Airport
+John F. Kennedy International Airport
+Josep Tarradellas Barcelona-El Prat Airport
+Kos International Airport "Ippokratis"
+Kraków John Paul II International Airport
+Larnaca International Airport
+Leipzig/Halle Airport
+London Gatwick Airport
+London Heathrow Airport
+Luxembourg-Findel International Airport
+Malta International Airport
+Marsa Alam International Airport
+Marseille Provence Airport
+Munich Airport
+Naples International Airport
+Narita International Airport
+Palma de Mallorca Airport
+Paphos International Airport
+Paris-Orly Airport
+Riga International Airport
+Rome–Fiumicino Leonardo da Vinci International Airport
+Sibiu International Airport
+Sofia Airport
+Stockholm-Arlanda Airport
+Stuttgart Airport
+Suvarnabhumi Airport
+Tirana International Airport Mother Teresa
+Venice Marco Polo Airport
+Vienna International Airport
+Warsaw Chopin Airport
+Zagreb Franjo Tuđman International Airport
+Zürich Airport
+İstanbul Airport</t>
   </si>
 </sst>
 </file>
@@ -1797,7 +1852,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1872,6 +1927,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -2190,12 +2246,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="A1" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2203,32 +2259,32 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2237,7 +2293,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B9" s="2"/>
     </row>
@@ -2246,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2254,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2262,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2270,7 +2326,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2278,7 +2334,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2286,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2294,15 +2350,15 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2310,15 +2366,15 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2327,32 +2383,32 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2361,24 +2417,24 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -4411,7 +4467,7 @@
         <v>280</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>281</v>
+        <v>533</v>
       </c>
       <c r="L55" s="13"/>
       <c r="M55" s="5"/>
@@ -4419,7 +4475,7 @@
     </row>
     <row r="56" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B56" s="18">
         <v>2</v>
@@ -4440,16 +4496,16 @@
         <v>128</v>
       </c>
       <c r="H56" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="I56" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I56" s="19" t="s">
+      <c r="J56" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="J56" s="19" t="s">
+      <c r="K56" s="19" t="s">
         <v>285</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>286</v>
       </c>
       <c r="L56" s="13"/>
       <c r="M56" s="5"/>
@@ -4457,13 +4513,13 @@
     </row>
     <row r="57" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B57" s="18">
         <v>2</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>105</v>
@@ -4472,22 +4528,22 @@
         <v>214</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G57" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H57" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="I57" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="I57" s="19" t="s">
+      <c r="J57" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="J57" s="19" t="s">
+      <c r="K57" s="19" t="s">
         <v>291</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>292</v>
       </c>
       <c r="L57" s="13"/>
       <c r="M57" s="5"/>
@@ -4495,13 +4551,13 @@
     </row>
     <row r="58" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B58" s="18">
         <v>2</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>105</v>
@@ -4510,22 +4566,22 @@
         <v>214</v>
       </c>
       <c r="F58" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G58" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H58" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="I58" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="I58" s="19" t="s">
+      <c r="J58" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="J58" s="19" t="s">
+      <c r="K58" s="19" t="s">
         <v>296</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>297</v>
       </c>
       <c r="L58" s="13"/>
       <c r="M58" s="5"/>
@@ -4533,13 +4589,13 @@
     </row>
     <row r="59" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B59" s="18">
         <v>2</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>59</v>
@@ -4548,22 +4604,22 @@
         <v>214</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G59" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H59" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="I59" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="I59" s="19" t="s">
+      <c r="J59" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="J59" s="19" t="s">
+      <c r="K59" s="19" t="s">
         <v>302</v>
-      </c>
-      <c r="K59" s="19" t="s">
-        <v>303</v>
       </c>
       <c r="L59" s="13"/>
       <c r="M59" s="5"/>
@@ -4571,13 +4627,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B60" s="18">
         <v>2</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>59</v>
@@ -4586,22 +4642,22 @@
         <v>214</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G60" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H60" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="I60" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="I60" s="19" t="s">
+      <c r="J60" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="J60" s="19" t="s">
+      <c r="K60" s="19" t="s">
         <v>307</v>
-      </c>
-      <c r="K60" s="19" t="s">
-        <v>308</v>
       </c>
       <c r="L60" s="13"/>
       <c r="M60" s="5"/>
@@ -4609,13 +4665,13 @@
     </row>
     <row r="61" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B61" s="18">
         <v>2</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>59</v>
@@ -4624,22 +4680,22 @@
         <v>214</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G61" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H61" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="I61" s="19" t="s">
         <v>310</v>
       </c>
-      <c r="I61" s="19" t="s">
+      <c r="J61" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="J61" s="19" t="s">
+      <c r="K61" s="19" t="s">
         <v>312</v>
-      </c>
-      <c r="K61" s="19" t="s">
-        <v>313</v>
       </c>
       <c r="L61" s="13"/>
       <c r="M61" s="5"/>
@@ -4647,13 +4703,13 @@
     </row>
     <row r="62" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B62" s="18">
         <v>2</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>59</v>
@@ -4662,22 +4718,22 @@
         <v>214</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G62" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H62" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="I62" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="I62" s="19" t="s">
+      <c r="J62" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="J62" s="19" t="s">
+      <c r="K62" s="19" t="s">
         <v>318</v>
-      </c>
-      <c r="K62" s="19" t="s">
-        <v>319</v>
       </c>
       <c r="L62" s="13"/>
       <c r="M62" s="5"/>
@@ -4685,13 +4741,13 @@
     </row>
     <row r="63" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B63" s="18">
         <v>2</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>59</v>
@@ -4700,22 +4756,22 @@
         <v>214</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G63" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H63" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="I63" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="I63" s="19" t="s">
+      <c r="J63" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="J63" s="19" t="s">
+      <c r="K63" s="19" t="s">
         <v>323</v>
-      </c>
-      <c r="K63" s="19" t="s">
-        <v>324</v>
       </c>
       <c r="L63" s="13"/>
       <c r="M63" s="5"/>
@@ -4723,13 +4779,13 @@
     </row>
     <row r="64" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B64" s="18">
         <v>2</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D64" s="18" t="s">
         <v>59</v>
@@ -4738,22 +4794,22 @@
         <v>214</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G64" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H64" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="I64" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="I64" s="19" t="s">
+      <c r="J64" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="J64" s="19" t="s">
+      <c r="K64" s="19" t="s">
         <v>328</v>
-      </c>
-      <c r="K64" s="19" t="s">
-        <v>329</v>
       </c>
       <c r="L64" s="13"/>
       <c r="M64" s="5"/>
@@ -4761,32 +4817,32 @@
     </row>
     <row r="65" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B65" s="18">
         <v>3</v>
       </c>
       <c r="C65" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="D65" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D65" s="18" t="s">
-        <v>332</v>
-      </c>
       <c r="E65" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F65" s="18"/>
       <c r="G65" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H65" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="I65" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="I65" s="19" t="s">
+      <c r="J65" s="19" t="s">
         <v>334</v>
-      </c>
-      <c r="J65" s="19" t="s">
-        <v>335</v>
       </c>
       <c r="K65" s="19"/>
       <c r="L65" s="13"/>
@@ -4795,32 +4851,32 @@
     </row>
     <row r="66" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B66" s="18">
         <v>3</v>
       </c>
       <c r="C66" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="D66" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D66" s="18" t="s">
-        <v>332</v>
-      </c>
       <c r="E66" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F66" s="18"/>
       <c r="G66" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H66" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="I66" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="I66" s="19" t="s">
+      <c r="J66" s="19" t="s">
         <v>338</v>
-      </c>
-      <c r="J66" s="19" t="s">
-        <v>339</v>
       </c>
       <c r="K66" s="19"/>
       <c r="L66" s="13"/>
@@ -4829,32 +4885,32 @@
     </row>
     <row r="67" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B67" s="18">
         <v>3</v>
       </c>
       <c r="C67" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="D67" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="18" t="s">
-        <v>332</v>
-      </c>
       <c r="E67" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F67" s="18"/>
       <c r="G67" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H67" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="I67" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="I67" s="19" t="s">
+      <c r="J67" s="19" t="s">
         <v>342</v>
-      </c>
-      <c r="J67" s="19" t="s">
-        <v>343</v>
       </c>
       <c r="K67" s="19"/>
       <c r="L67" s="13"/>
@@ -4863,35 +4919,35 @@
     </row>
     <row r="68" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B68" s="18">
         <v>3</v>
       </c>
       <c r="C68" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D68" s="18" t="s">
-        <v>346</v>
-      </c>
       <c r="E68" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F68" s="18"/>
       <c r="G68" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H68" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="I68" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="I68" s="19" t="s">
+      <c r="J68" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="J68" s="19" t="s">
+      <c r="K68" s="19" t="s">
         <v>349</v>
-      </c>
-      <c r="K68" s="19" t="s">
-        <v>350</v>
       </c>
       <c r="L68" s="13"/>
       <c r="M68" s="5"/>
@@ -4899,35 +4955,35 @@
     </row>
     <row r="69" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B69" s="18">
         <v>3</v>
       </c>
       <c r="C69" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="D69" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D69" s="18" t="s">
-        <v>346</v>
-      </c>
       <c r="E69" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F69" s="18"/>
       <c r="G69" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H69" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="I69" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="I69" s="19" t="s">
+      <c r="J69" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="J69" s="19" t="s">
-        <v>354</v>
-      </c>
       <c r="K69" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L69" s="13"/>
       <c r="M69" s="5"/>
@@ -4935,35 +4991,35 @@
     </row>
     <row r="70" spans="1:14" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B70" s="18">
         <v>3</v>
       </c>
       <c r="C70" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="D70" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D70" s="18" t="s">
-        <v>346</v>
-      </c>
       <c r="E70" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H70" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="I70" s="19" t="s">
         <v>356</v>
       </c>
-      <c r="I70" s="19" t="s">
+      <c r="J70" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="J70" s="19" t="s">
+      <c r="K70" s="19" t="s">
         <v>358</v>
-      </c>
-      <c r="K70" s="19" t="s">
-        <v>359</v>
       </c>
       <c r="L70" s="13"/>
       <c r="M70" s="5"/>
@@ -4971,35 +5027,35 @@
     </row>
     <row r="71" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B71" s="18">
         <v>3</v>
       </c>
       <c r="C71" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="D71" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D71" s="18" t="s">
-        <v>346</v>
-      </c>
       <c r="E71" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H71" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="I71" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="I71" s="19" t="s">
+      <c r="J71" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="J71" s="19" t="s">
-        <v>363</v>
-      </c>
       <c r="K71" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L71" s="13"/>
       <c r="M71" s="5"/>
@@ -5007,35 +5063,35 @@
     </row>
     <row r="72" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B72" s="18">
         <v>3</v>
       </c>
       <c r="C72" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="E72" s="18" t="s">
         <v>365</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>366</v>
       </c>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H72" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="I72" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="I72" s="19" t="s">
+      <c r="J72" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="J72" s="19" t="s">
+      <c r="K72" s="19" t="s">
         <v>369</v>
-      </c>
-      <c r="K72" s="19" t="s">
-        <v>370</v>
       </c>
       <c r="L72" s="13"/>
       <c r="M72" s="5"/>
@@ -5043,35 +5099,35 @@
     </row>
     <row r="73" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B73" s="18">
         <v>3</v>
       </c>
       <c r="C73" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="E73" s="18" t="s">
         <v>365</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>366</v>
       </c>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H73" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="I73" s="19" t="s">
         <v>372</v>
-      </c>
-      <c r="I73" s="19" t="s">
-        <v>373</v>
       </c>
       <c r="J73" s="19" t="s">
         <v>32</v>
       </c>
       <c r="K73" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L73" s="13"/>
       <c r="M73" s="5"/>
@@ -5079,29 +5135,29 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B74" s="18">
         <v>3</v>
       </c>
       <c r="C74" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="E74" s="18" t="s">
         <v>365</v>
-      </c>
-      <c r="D74" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="E74" s="18" t="s">
-        <v>366</v>
       </c>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H74" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I74" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="I74" s="19" t="s">
-        <v>377</v>
       </c>
       <c r="J74" s="19" t="s">
         <v>82</v>
@@ -5115,35 +5171,35 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B75" s="18">
         <v>3</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H75" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="I75" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="I75" s="19" t="s">
-        <v>381</v>
-      </c>
       <c r="J75" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="K75" s="19" t="s">
         <v>369</v>
-      </c>
-      <c r="K75" s="19" t="s">
-        <v>370</v>
       </c>
       <c r="L75" s="13"/>
       <c r="M75" s="5"/>
@@ -5151,32 +5207,32 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B76" s="18">
         <v>3</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F76" s="18"/>
       <c r="G76" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H76" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="I76" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="I76" s="19" t="s">
+      <c r="J76" s="19" t="s">
         <v>384</v>
-      </c>
-      <c r="J76" s="19" t="s">
-        <v>385</v>
       </c>
       <c r="K76" s="19" t="s">
         <v>160</v>
@@ -5187,35 +5243,35 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B77" s="18">
         <v>3</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F77" s="18"/>
       <c r="G77" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H77" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="I77" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="I77" s="19" t="s">
+      <c r="J77" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="J77" s="19" t="s">
-        <v>389</v>
-      </c>
       <c r="K77" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L77" s="13"/>
       <c r="M77" s="5"/>
@@ -5223,35 +5279,35 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="18" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B78" s="18">
         <v>3</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H78" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="I78" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="I78" s="19" t="s">
+      <c r="J78" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="J78" s="19" t="s">
+      <c r="K78" s="19" t="s">
         <v>393</v>
-      </c>
-      <c r="K78" s="19" t="s">
-        <v>394</v>
       </c>
       <c r="L78" s="13"/>
       <c r="M78" s="5"/>
@@ -5259,35 +5315,35 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B79" s="18">
         <v>3</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F79" s="18"/>
       <c r="G79" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H79" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="I79" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="I79" s="19" t="s">
+      <c r="J79" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="J79" s="19" t="s">
+      <c r="K79" s="22" t="s">
         <v>399</v>
-      </c>
-      <c r="K79" s="22" t="s">
-        <v>400</v>
       </c>
       <c r="L79" s="13"/>
       <c r="M79" s="5"/>
@@ -5295,35 +5351,35 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B80" s="18">
         <v>3</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F80" s="18"/>
       <c r="G80" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H80" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="I80" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="I80" s="19" t="s">
+      <c r="J80" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="J80" s="19" t="s">
+      <c r="K80" s="19" t="s">
         <v>404</v>
-      </c>
-      <c r="K80" s="19" t="s">
-        <v>405</v>
       </c>
       <c r="L80" s="13"/>
       <c r="M80" s="5"/>
@@ -5331,35 +5387,35 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B81" s="18">
         <v>3</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F81" s="18"/>
       <c r="G81" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H81" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="I81" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="I81" s="19" t="s">
+      <c r="J81" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="J81" s="19" t="s">
-        <v>409</v>
-      </c>
       <c r="K81" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L81" s="13"/>
       <c r="M81" s="5"/>
@@ -5367,35 +5423,35 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="18" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B82" s="18">
         <v>3</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="18" t="s">
         <v>128</v>
       </c>
       <c r="H82" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I82" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="I82" s="19" t="s">
+      <c r="J82" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="J82" s="19" t="s">
-        <v>413</v>
-      </c>
       <c r="K82" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L82" s="13"/>
       <c r="M82" s="5"/>
@@ -5403,7 +5459,7 @@
     </row>
     <row r="83" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B83" s="23">
         <v>1</v>
@@ -5422,16 +5478,16 @@
         <v>14</v>
       </c>
       <c r="H83" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="I83" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="I83" s="24" t="s">
+      <c r="J83" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="J83" s="24" t="s">
-        <v>417</v>
-      </c>
       <c r="K83" s="24" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
@@ -5439,7 +5495,7 @@
     </row>
     <row r="84" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B84" s="23">
         <v>1</v>
@@ -5458,13 +5514,13 @@
         <v>14</v>
       </c>
       <c r="H84" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="I84" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="I84" s="24" t="s">
+      <c r="J84" s="24" t="s">
         <v>420</v>
-      </c>
-      <c r="J84" s="24" t="s">
-        <v>421</v>
       </c>
       <c r="K84" s="24">
         <v>397</v>
@@ -5475,7 +5531,7 @@
     </row>
     <row r="85" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B85" s="23">
         <v>1</v>
@@ -5494,13 +5550,13 @@
         <v>14</v>
       </c>
       <c r="H85" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="I85" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="I85" s="24" t="s">
+      <c r="J85" s="24" t="s">
         <v>424</v>
-      </c>
-      <c r="J85" s="24" t="s">
-        <v>425</v>
       </c>
       <c r="K85" s="24">
         <v>2048</v>
@@ -5511,7 +5567,7 @@
     </row>
     <row r="86" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B86" s="23">
         <v>1</v>
@@ -5530,16 +5586,16 @@
         <v>14</v>
       </c>
       <c r="H86" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="I86" s="24" t="s">
         <v>427</v>
       </c>
-      <c r="I86" s="24" t="s">
+      <c r="J86" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="J86" s="24" t="s">
-        <v>429</v>
-      </c>
       <c r="K86" s="24" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
@@ -5547,7 +5603,7 @@
     </row>
     <row r="87" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B87" s="23">
         <v>1</v>
@@ -5566,13 +5622,13 @@
         <v>14</v>
       </c>
       <c r="H87" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="I87" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="I87" s="24" t="s">
+      <c r="J87" s="24" t="s">
         <v>432</v>
-      </c>
-      <c r="J87" s="24" t="s">
-        <v>433</v>
       </c>
       <c r="K87" s="24">
         <v>13123</v>
@@ -5583,7 +5639,7 @@
     </row>
     <row r="88" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B88" s="23">
         <v>1</v>
@@ -5602,16 +5658,16 @@
         <v>14</v>
       </c>
       <c r="H88" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="I88" s="24" t="s">
         <v>435</v>
       </c>
-      <c r="I88" s="24" t="s">
-        <v>436</v>
-      </c>
       <c r="J88" s="24" t="s">
-        <v>437</v>
+        <v>531</v>
       </c>
       <c r="K88" s="24" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
@@ -5619,7 +5675,7 @@
     </row>
     <row r="89" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B89" s="23">
         <v>1</v>
@@ -5638,13 +5694,13 @@
         <v>14</v>
       </c>
       <c r="H89" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="I89" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="J89" s="24" t="s">
         <v>439</v>
-      </c>
-      <c r="I89" s="24" t="s">
-        <v>440</v>
-      </c>
-      <c r="J89" s="24" t="s">
-        <v>441</v>
       </c>
       <c r="K89" s="24" t="s">
         <v>93</v>
@@ -5655,7 +5711,7 @@
     </row>
     <row r="90" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="23" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B90" s="23">
         <v>1</v>
@@ -5674,16 +5730,16 @@
         <v>14</v>
       </c>
       <c r="H90" s="24" t="s">
+        <v>441</v>
+      </c>
+      <c r="I90" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="J90" s="24" t="s">
         <v>443</v>
       </c>
-      <c r="I90" s="24" t="s">
-        <v>444</v>
-      </c>
-      <c r="J90" s="24" t="s">
-        <v>445</v>
-      </c>
       <c r="K90" s="24" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
@@ -5691,7 +5747,7 @@
     </row>
     <row r="91" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="23" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B91" s="23">
         <v>1</v>
@@ -5710,16 +5766,16 @@
         <v>14</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I91" s="24" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J91" s="24" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K91" s="24" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="26"/>
@@ -5727,7 +5783,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="23" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B92" s="23">
         <v>1</v>
@@ -5746,16 +5802,16 @@
         <v>14</v>
       </c>
       <c r="H92" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="J92" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="K92" s="27" t="s">
         <v>518</v>
-      </c>
-      <c r="I92" s="24" t="s">
-        <v>519</v>
-      </c>
-      <c r="J92" s="24" t="s">
-        <v>520</v>
-      </c>
-      <c r="K92" s="27" t="s">
-        <v>521</v>
       </c>
       <c r="L92" s="25"/>
       <c r="M92" s="26"/>
@@ -5763,7 +5819,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="23" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B93" s="23">
         <v>1</v>
@@ -5782,15 +5838,15 @@
         <v>14</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="I93" s="24" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J93" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="K93" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="K93" s="28" t="s">
         <v>530</v>
       </c>
       <c r="L93" s="25"/>
@@ -5799,7 +5855,7 @@
     </row>
     <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="23" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B94" s="23">
         <v>1</v>
@@ -5818,13 +5874,13 @@
         <v>14</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I94" s="24" t="s">
-        <v>453</v>
+        <v>532</v>
       </c>
       <c r="J94" s="24" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K94" s="24" t="s">
         <v>132</v>
@@ -5835,7 +5891,7 @@
     </row>
     <row r="95" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="23" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B95" s="23">
         <v>1</v>
@@ -5854,13 +5910,13 @@
         <v>14</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I95" s="24" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J95" s="24" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K95" s="24">
         <v>325</v>
@@ -5871,7 +5927,7 @@
     </row>
     <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="23" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B96" s="23">
         <v>1</v>
@@ -5890,13 +5946,13 @@
         <v>14</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J96" s="24" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="K96" s="24" t="s">
         <v>93</v>
@@ -5907,13 +5963,13 @@
     </row>
     <row r="97" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="23" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B97" s="23">
         <v>2</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D97" s="23" t="s">
         <v>59</v>
@@ -5922,22 +5978,22 @@
         <v>214</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G97" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="I97" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="J97" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="K97" s="24" t="s">
         <v>523</v>
-      </c>
-      <c r="J97" s="24" t="s">
-        <v>524</v>
-      </c>
-      <c r="K97" s="24" t="s">
-        <v>526</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
@@ -5945,13 +6001,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="23" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B98" s="23">
         <v>2</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D98" s="23" t="s">
         <v>105</v>
@@ -5960,22 +6016,22 @@
         <v>214</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G98" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J98" s="24" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="K98" s="24">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
@@ -5983,13 +6039,13 @@
     </row>
     <row r="99" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="23" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B99" s="23">
         <v>2</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D99" s="23" t="s">
         <v>59</v>
@@ -5998,22 +6054,22 @@
         <v>214</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G99" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I99" s="24" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J99" s="24" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K99" s="24" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
@@ -6021,35 +6077,35 @@
     </row>
     <row r="100" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="23" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B100" s="23">
         <v>3</v>
       </c>
       <c r="C100" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="D100" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="D100" s="23" t="s">
-        <v>346</v>
-      </c>
       <c r="E100" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F100" s="23"/>
       <c r="G100" s="23" t="s">
         <v>128</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I100" s="24" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J100" s="24" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="K100" s="24" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
@@ -6057,7 +6113,7 @@
     </row>
     <row r="101" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B101" s="23">
         <v>1</v>
@@ -6076,13 +6132,13 @@
         <v>14</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I101" s="24" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J101" s="24" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K101" s="24">
         <v>58</v>
@@ -6168,7 +6224,7 @@
     <hyperlink ref="K72" r:id="rId2" display="www.University0.edu" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="K73" r:id="rId3" display="www.University0.edu" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="K92" r:id="rId4" xr:uid="{F402B207-9C31-4349-83A1-BCC6F56AEDB2}"/>
-    <hyperlink ref="K93" r:id="rId5" display="www.University0.edu" xr:uid="{68DBCBB5-52F3-45C1-8520-C539E611CD0B}"/>
+    <hyperlink ref="K93" r:id="rId5" xr:uid="{68DBCBB5-52F3-45C1-8520-C539E611CD0B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F28320-D23C-49EC-BDBF-7B5756C8BBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E78230-DB48-4D50-9B94-CA6063FDD230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9168B783-BC61-4F99-8B87-105DF4703FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0967C3E6-BF12-494C-B334-BA58677C23DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="629">
   <si>
     <t>id</t>
   </si>
@@ -1697,21 +1697,6 @@
   </si>
   <si>
     <t>Department14 (376), Department6 (405)</t>
-  </si>
-  <si>
-    <t>filter_numeric_kg3_003</t>
-  </si>
-  <si>
-    <t>Which departments have a total headcount somewhere between 500 and 580 people, not counting the very largest or smallest ones?</t>
-  </si>
-  <si>
-    <t>Quels départements comptent un effectif total compris entre 500 et 580 personnes, sans compter les plus grands ni les plus petits ?</t>
-  </si>
-  <si>
-    <t>ما هي الأقسام التي يتراوح عدد أفرادها الإجمالي بين 500 و580 شخصًا، دون احتساب الأكبر أو الأصغر؟</t>
-  </si>
-  <si>
-    <t>Department8 (579), Department5 (554), Department10 (549), Department4 (544), Department11 (530), Department1 (521)</t>
   </si>
   <si>
     <t>single_kg3_010</t>
@@ -2151,8 +2136,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2196,6 +2179,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2513,12 +2498,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="A1" s="28" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2526,32 +2511,32 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2560,7 +2545,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B9" s="2"/>
     </row>
@@ -2569,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2577,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2585,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2593,7 +2578,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2601,7 +2586,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,7 +2594,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,15 +2602,15 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2633,15 +2618,15 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2650,32 +2635,32 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2684,24 +2669,24 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>
@@ -2714,63 +2699,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" style="19" customWidth="1"/>
-    <col min="2" max="2" width="12" style="19" customWidth="1"/>
-    <col min="3" max="3" width="22" style="19" customWidth="1"/>
-    <col min="4" max="4" width="12" style="19" customWidth="1"/>
-    <col min="5" max="5" width="16" style="19" customWidth="1"/>
-    <col min="6" max="6" width="20" style="19" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" style="19" customWidth="1"/>
-    <col min="8" max="9" width="46" style="19" customWidth="1"/>
-    <col min="10" max="10" width="79.42578125" style="19" customWidth="1"/>
-    <col min="11" max="11" width="46.42578125" style="19" customWidth="1"/>
-    <col min="12" max="12" width="64.5703125" style="25" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="29"/>
-    <col min="14" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="25" style="17" customWidth="1"/>
+    <col min="2" max="2" width="12" style="17" customWidth="1"/>
+    <col min="3" max="3" width="22" style="17" customWidth="1"/>
+    <col min="4" max="4" width="12" style="17" customWidth="1"/>
+    <col min="5" max="5" width="16" style="17" customWidth="1"/>
+    <col min="6" max="6" width="20" style="17" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="17" customWidth="1"/>
+    <col min="8" max="9" width="46" style="17" customWidth="1"/>
+    <col min="10" max="10" width="79.42578125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="46.42578125" style="17" customWidth="1"/>
+    <col min="12" max="12" width="64.5703125" style="23" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="27"/>
+    <col min="14" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:14" s="15" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="4"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="16"/>
-    </row>
-    <row r="2" spans="1:14" s="18" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="26"/>
+      <c r="N1" s="14"/>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -2803,27 +2788,27 @@
         <v>18</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="21"/>
+      <c r="M2" s="19"/>
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="12">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="6" t="s">
@@ -2839,27 +2824,27 @@
         <v>23</v>
       </c>
       <c r="L3" s="6"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="6" t="s">
@@ -2875,27 +2860,27 @@
         <v>28</v>
       </c>
       <c r="L4" s="6"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H5" s="6" t="s">
@@ -2911,27 +2896,27 @@
         <v>33</v>
       </c>
       <c r="L5" s="6"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="17"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="6" t="s">
@@ -2947,27 +2932,27 @@
         <v>38</v>
       </c>
       <c r="L6" s="6"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="6" t="s">
@@ -2983,27 +2968,27 @@
         <v>43</v>
       </c>
       <c r="L7" s="6"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <v>1</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="6" t="s">
@@ -3019,27 +3004,27 @@
         <v>18</v>
       </c>
       <c r="L8" s="6"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <v>1</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="6" t="s">
@@ -3055,27 +3040,27 @@
         <v>18</v>
       </c>
       <c r="L9" s="6"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="12">
         <v>1</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="6" t="s">
@@ -3091,8 +3076,8 @@
         <v>56</v>
       </c>
       <c r="L10" s="6"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -3127,27 +3112,27 @@
         <v>63</v>
       </c>
       <c r="L11" s="7"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="12">
         <v>1</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="6" t="s">
@@ -3163,27 +3148,27 @@
         <v>68</v>
       </c>
       <c r="L12" s="6"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <v>1</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14" t="s">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H13" s="6" t="s">
@@ -3199,27 +3184,27 @@
         <v>73</v>
       </c>
       <c r="L13" s="6"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <v>1</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14" t="s">
+      <c r="F14" s="12"/>
+      <c r="G14" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="6" t="s">
@@ -3235,27 +3220,27 @@
         <v>78</v>
       </c>
       <c r="L14" s="6"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="12">
         <v>1</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H15" s="6" t="s">
@@ -3271,27 +3256,27 @@
         <v>83</v>
       </c>
       <c r="L15" s="6"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="s">
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="6" t="s">
@@ -3307,27 +3292,27 @@
         <v>88</v>
       </c>
       <c r="L16" s="6"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="12">
         <v>1</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14" t="s">
+      <c r="F17" s="12"/>
+      <c r="G17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H17" s="6" t="s">
@@ -3343,27 +3328,27 @@
         <v>93</v>
       </c>
       <c r="L17" s="6"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <v>1</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14" t="s">
+      <c r="F18" s="12"/>
+      <c r="G18" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="6" t="s">
@@ -3379,27 +3364,27 @@
         <v>73</v>
       </c>
       <c r="L18" s="6"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="12">
         <v>1</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14" t="s">
+      <c r="F19" s="12"/>
+      <c r="G19" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="6" t="s">
@@ -3415,8 +3400,8 @@
         <v>102</v>
       </c>
       <c r="L19" s="6"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -3451,8 +3436,8 @@
         <v>109</v>
       </c>
       <c r="L20" s="7"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -3487,8 +3472,8 @@
         <v>114</v>
       </c>
       <c r="L21" s="7"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
@@ -3523,8 +3508,8 @@
         <v>119</v>
       </c>
       <c r="L22" s="7"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
@@ -3559,8 +3544,8 @@
         <v>124</v>
       </c>
       <c r="L23" s="7"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -3595,27 +3580,27 @@
         <v>132</v>
       </c>
       <c r="L24" s="7"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="12">
         <v>1</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14" t="s">
+      <c r="F25" s="12"/>
+      <c r="G25" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H25" s="6" t="s">
@@ -3631,27 +3616,27 @@
         <v>137</v>
       </c>
       <c r="L25" s="6"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="12">
         <v>1</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14" t="s">
+      <c r="F26" s="12"/>
+      <c r="G26" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H26" s="6" t="s">
@@ -3667,27 +3652,27 @@
         <v>142</v>
       </c>
       <c r="L26" s="6"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="12">
         <v>1</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14" t="s">
+      <c r="F27" s="12"/>
+      <c r="G27" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H27" s="6" t="s">
@@ -3703,27 +3688,27 @@
         <v>93</v>
       </c>
       <c r="L27" s="6"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="12">
         <v>1</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14" t="s">
+      <c r="F28" s="12"/>
+      <c r="G28" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H28" s="6" t="s">
@@ -3739,27 +3724,27 @@
         <v>83</v>
       </c>
       <c r="L28" s="6"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="12">
         <v>1</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14" t="s">
+      <c r="F29" s="12"/>
+      <c r="G29" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H29" s="6" t="s">
@@ -3775,27 +3760,27 @@
         <v>155</v>
       </c>
       <c r="L29" s="6"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="12">
         <v>1</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="12"/>
+      <c r="G30" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H30" s="6" t="s">
@@ -3811,27 +3796,27 @@
         <v>160</v>
       </c>
       <c r="L30" s="6"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="12">
         <v>1</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14" t="s">
+      <c r="F31" s="12"/>
+      <c r="G31" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H31" s="6" t="s">
@@ -3847,27 +3832,27 @@
         <v>93</v>
       </c>
       <c r="L31" s="6"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="12">
         <v>1</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14" t="s">
+      <c r="F32" s="12"/>
+      <c r="G32" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H32" s="6" t="s">
@@ -3883,27 +3868,27 @@
         <v>169</v>
       </c>
       <c r="L32" s="6"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="12">
         <v>1</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14" t="s">
+      <c r="F33" s="12"/>
+      <c r="G33" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H33" s="6" t="s">
@@ -3919,27 +3904,27 @@
         <v>73</v>
       </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="12">
         <v>1</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14" t="s">
+      <c r="F34" s="12"/>
+      <c r="G34" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
@@ -3955,27 +3940,27 @@
         <v>178</v>
       </c>
       <c r="L34" s="6"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="12">
         <v>1</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="s">
+      <c r="F35" s="12"/>
+      <c r="G35" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="6" t="s">
@@ -3991,27 +3976,27 @@
         <v>93</v>
       </c>
       <c r="L35" s="6"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="12">
         <v>1</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="s">
+      <c r="F36" s="12"/>
+      <c r="G36" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
@@ -4027,27 +4012,27 @@
         <v>188</v>
       </c>
       <c r="L36" s="6"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="12">
         <v>1</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
+      <c r="F37" s="12"/>
+      <c r="G37" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H37" s="6" t="s">
@@ -4063,27 +4048,27 @@
         <v>4</v>
       </c>
       <c r="L37" s="6"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="12">
         <v>1</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14" t="s">
+      <c r="F38" s="12"/>
+      <c r="G38" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
@@ -4099,27 +4084,27 @@
         <v>6</v>
       </c>
       <c r="L38" s="6"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="12">
         <v>1</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14" t="s">
+      <c r="F39" s="12"/>
+      <c r="G39" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H39" s="6" t="s">
@@ -4135,27 +4120,27 @@
         <v>201</v>
       </c>
       <c r="L39" s="6"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B40" s="12">
         <v>1</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14" t="s">
+      <c r="F40" s="12"/>
+      <c r="G40" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H40" s="6" t="s">
@@ -4171,27 +4156,27 @@
         <v>206</v>
       </c>
       <c r="L40" s="6"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="12">
         <v>1</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14" t="s">
+      <c r="F41" s="12"/>
+      <c r="G41" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H41" s="6" t="s">
@@ -4207,29 +4192,29 @@
         <v>211</v>
       </c>
       <c r="L41" s="6"/>
-      <c r="M41" s="21"/>
-      <c r="N41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="12">
         <v>2</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H42" s="6" t="s">
@@ -4245,29 +4230,29 @@
         <v>45</v>
       </c>
       <c r="L42" s="6"/>
-      <c r="M42" s="21"/>
-      <c r="N42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="12">
         <v>2</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H43" s="6" t="s">
@@ -4283,29 +4268,29 @@
         <v>61</v>
       </c>
       <c r="L43" s="6"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="12">
         <v>2</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
@@ -4321,29 +4306,29 @@
         <v>57</v>
       </c>
       <c r="L44" s="6"/>
-      <c r="M44" s="21"/>
-      <c r="N44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="12">
         <v>2</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H45" s="6" t="s">
@@ -4359,29 +4344,29 @@
         <v>3</v>
       </c>
       <c r="L45" s="6"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="12">
         <v>2</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H46" s="6" t="s">
@@ -4397,29 +4382,29 @@
         <v>2</v>
       </c>
       <c r="L46" s="6"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="12">
         <v>2</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H47" s="6" t="s">
@@ -4435,29 +4420,29 @@
         <v>41</v>
       </c>
       <c r="L47" s="6"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="12">
         <v>2</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -4473,29 +4458,29 @@
         <v>244</v>
       </c>
       <c r="L48" s="6"/>
-      <c r="M48" s="21"/>
-      <c r="N48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="12">
         <v>2</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H49" s="6" t="s">
@@ -4511,29 +4496,29 @@
         <v>249</v>
       </c>
       <c r="L49" s="6"/>
-      <c r="M49" s="21"/>
-      <c r="N49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="12">
         <v>2</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H50" s="6" t="s">
@@ -4549,29 +4534,29 @@
         <v>254</v>
       </c>
       <c r="L50" s="6"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="12">
         <v>2</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H51" s="6" t="s">
@@ -4587,29 +4572,29 @@
         <v>260</v>
       </c>
       <c r="L51" s="6"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="12">
         <v>2</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="G52" s="14" t="s">
+      <c r="G52" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H52" s="6" t="s">
@@ -4625,29 +4610,29 @@
         <v>265</v>
       </c>
       <c r="L52" s="6"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="12">
         <v>2</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H53" s="6" t="s">
@@ -4663,29 +4648,29 @@
         <v>270</v>
       </c>
       <c r="L53" s="6"/>
-      <c r="M53" s="21"/>
-      <c r="N53" s="19"/>
+      <c r="M53" s="19"/>
+      <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="12">
         <v>2</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G54" s="14" t="s">
+      <c r="G54" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H54" s="6" t="s">
@@ -4701,29 +4686,29 @@
         <v>276</v>
       </c>
       <c r="L54" s="6"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="19"/>
+      <c r="M54" s="19"/>
+      <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="12">
         <v>2</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G55" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H55" s="6" t="s">
@@ -4739,29 +4724,29 @@
         <v>281</v>
       </c>
       <c r="L55" s="6"/>
-      <c r="M55" s="21"/>
-      <c r="N55" s="19"/>
+      <c r="M55" s="19"/>
+      <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="12">
         <v>2</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="G56" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H56" s="6" t="s">
@@ -4777,29 +4762,29 @@
         <v>286</v>
       </c>
       <c r="L56" s="6"/>
-      <c r="M56" s="21"/>
-      <c r="N56" s="19"/>
+      <c r="M56" s="19"/>
+      <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="B57" s="14">
+      <c r="B57" s="12">
         <v>2</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="G57" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H57" s="6" t="s">
@@ -4815,29 +4800,29 @@
         <v>292</v>
       </c>
       <c r="L57" s="6"/>
-      <c r="M57" s="21"/>
-      <c r="N57" s="19"/>
+      <c r="M57" s="19"/>
+      <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="B58" s="14">
+      <c r="B58" s="12">
         <v>2</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="G58" s="14" t="s">
+      <c r="G58" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H58" s="6" t="s">
@@ -4853,29 +4838,29 @@
         <v>297</v>
       </c>
       <c r="L58" s="6"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="19"/>
+      <c r="M58" s="19"/>
+      <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B59" s="14">
+      <c r="B59" s="12">
         <v>2</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="G59" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H59" s="6" t="s">
@@ -4891,29 +4876,29 @@
         <v>303</v>
       </c>
       <c r="L59" s="6"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="19"/>
+      <c r="M59" s="19"/>
+      <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B60" s="14">
+      <c r="B60" s="12">
         <v>2</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="G60" s="14" t="s">
+      <c r="G60" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H60" s="6" t="s">
@@ -4929,29 +4914,29 @@
         <v>308</v>
       </c>
       <c r="L60" s="6"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="19"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="B61" s="14">
+      <c r="B61" s="12">
         <v>2</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G61" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H61" s="6" t="s">
@@ -4967,29 +4952,29 @@
         <v>313</v>
       </c>
       <c r="L61" s="6"/>
-      <c r="M61" s="21"/>
-      <c r="N61" s="19"/>
+      <c r="M61" s="19"/>
+      <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="B62" s="14">
+      <c r="B62" s="12">
         <v>2</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="G62" s="14" t="s">
+      <c r="G62" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H62" s="6" t="s">
@@ -5005,29 +4990,29 @@
         <v>319</v>
       </c>
       <c r="L62" s="6"/>
-      <c r="M62" s="21"/>
-      <c r="N62" s="19"/>
+      <c r="M62" s="19"/>
+      <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B63" s="14">
+      <c r="B63" s="12">
         <v>2</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="G63" s="14" t="s">
+      <c r="G63" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H63" s="6" t="s">
@@ -5043,29 +5028,29 @@
         <v>324</v>
       </c>
       <c r="L63" s="6"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="19"/>
+      <c r="M63" s="19"/>
+      <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="B64" s="14">
+      <c r="B64" s="12">
         <v>2</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="G64" s="14" t="s">
+      <c r="G64" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H64" s="6" t="s">
@@ -5081,27 +5066,27 @@
         <v>329</v>
       </c>
       <c r="L64" s="6"/>
-      <c r="M64" s="21"/>
-      <c r="N64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="B65" s="14">
+      <c r="B65" s="12">
         <v>3</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14" t="s">
+      <c r="F65" s="12"/>
+      <c r="G65" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H65" s="6" t="s">
@@ -5115,27 +5100,27 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
-      <c r="M65" s="21"/>
-      <c r="N65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B66" s="14">
+      <c r="B66" s="12">
         <v>3</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14" t="s">
+      <c r="F66" s="12"/>
+      <c r="G66" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H66" s="6" t="s">
@@ -5149,27 +5134,27 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
-      <c r="M66" s="21"/>
-      <c r="N66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B67" s="14">
+      <c r="B67" s="12">
         <v>3</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D67" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14" t="s">
+      <c r="F67" s="12"/>
+      <c r="G67" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H67" s="6" t="s">
@@ -5183,27 +5168,27 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
-      <c r="M67" s="21"/>
-      <c r="N67" s="19"/>
+      <c r="M67" s="19"/>
+      <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B68" s="14">
+      <c r="B68" s="12">
         <v>3</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14" t="s">
+      <c r="F68" s="12"/>
+      <c r="G68" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H68" s="6" t="s">
@@ -5219,27 +5204,27 @@
         <v>350</v>
       </c>
       <c r="L68" s="6"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="19"/>
+      <c r="M68" s="19"/>
+      <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="B69" s="14">
+      <c r="B69" s="12">
         <v>3</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14" t="s">
+      <c r="F69" s="12"/>
+      <c r="G69" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H69" s="6" t="s">
@@ -5255,27 +5240,27 @@
         <v>350</v>
       </c>
       <c r="L69" s="6"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="19"/>
+      <c r="M69" s="19"/>
+      <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B70" s="14">
+      <c r="B70" s="12">
         <v>3</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14" t="s">
+      <c r="F70" s="12"/>
+      <c r="G70" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H70" s="6" t="s">
@@ -5291,27 +5276,27 @@
         <v>359</v>
       </c>
       <c r="L70" s="6"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="19"/>
+      <c r="M70" s="19"/>
+      <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B71" s="14">
+      <c r="B71" s="12">
         <v>3</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14" t="s">
+      <c r="F71" s="12"/>
+      <c r="G71" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H71" s="6" t="s">
@@ -5327,27 +5312,27 @@
         <v>359</v>
       </c>
       <c r="L71" s="6"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="19"/>
+      <c r="M71" s="19"/>
+      <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="B72" s="14">
+      <c r="B72" s="12">
         <v>3</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14" t="s">
+      <c r="F72" s="12"/>
+      <c r="G72" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H72" s="6" t="s">
@@ -5363,27 +5348,27 @@
         <v>370</v>
       </c>
       <c r="L72" s="6"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B73" s="14">
+      <c r="B73" s="12">
         <v>3</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14" t="s">
+      <c r="F73" s="12"/>
+      <c r="G73" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H73" s="6" t="s">
@@ -5399,27 +5384,27 @@
         <v>374</v>
       </c>
       <c r="L73" s="6"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="19"/>
+      <c r="M73" s="19"/>
+      <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="B74" s="14">
+      <c r="B74" s="12">
         <v>3</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E74" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14" t="s">
+      <c r="F74" s="12"/>
+      <c r="G74" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H74" s="6" t="s">
@@ -5435,27 +5420,27 @@
         <v>83</v>
       </c>
       <c r="L74" s="6"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="19"/>
+      <c r="M74" s="19"/>
+      <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="B75" s="14">
+      <c r="B75" s="12">
         <v>3</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14" t="s">
+      <c r="F75" s="12"/>
+      <c r="G75" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H75" s="6" t="s">
@@ -5471,27 +5456,27 @@
         <v>370</v>
       </c>
       <c r="L75" s="6"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="19"/>
+      <c r="M75" s="19"/>
+      <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="B76" s="14">
+      <c r="B76" s="12">
         <v>3</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14" t="s">
+      <c r="F76" s="12"/>
+      <c r="G76" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H76" s="6" t="s">
@@ -5507,27 +5492,27 @@
         <v>160</v>
       </c>
       <c r="L76" s="6"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="19"/>
+      <c r="M76" s="19"/>
+      <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="12">
         <v>3</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14" t="s">
+      <c r="F77" s="12"/>
+      <c r="G77" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H77" s="6" t="s">
@@ -5543,27 +5528,27 @@
         <v>350</v>
       </c>
       <c r="L77" s="6"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="19"/>
+      <c r="M77" s="19"/>
+      <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="B78" s="14">
+      <c r="B78" s="12">
         <v>3</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="D78" s="14" t="s">
+      <c r="D78" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14" t="s">
+      <c r="F78" s="12"/>
+      <c r="G78" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H78" s="6" t="s">
@@ -5579,27 +5564,27 @@
         <v>394</v>
       </c>
       <c r="L78" s="6"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="19"/>
+      <c r="M78" s="19"/>
+      <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="B79" s="14">
+      <c r="B79" s="12">
         <v>3</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D79" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14" t="s">
+      <c r="F79" s="12"/>
+      <c r="G79" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H79" s="6" t="s">
@@ -5615,27 +5600,27 @@
         <v>400</v>
       </c>
       <c r="L79" s="6"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="19"/>
+      <c r="M79" s="19"/>
+      <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="B80" s="14">
+      <c r="B80" s="12">
         <v>3</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14" t="s">
+      <c r="F80" s="12"/>
+      <c r="G80" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H80" s="6" t="s">
@@ -5651,27 +5636,27 @@
         <v>405</v>
       </c>
       <c r="L80" s="6"/>
-      <c r="M80" s="21"/>
-      <c r="N80" s="19"/>
+      <c r="M80" s="19"/>
+      <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="B81" s="14">
+      <c r="B81" s="12">
         <v>3</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="D81" s="14" t="s">
+      <c r="D81" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E81" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14" t="s">
+      <c r="F81" s="12"/>
+      <c r="G81" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H81" s="6" t="s">
@@ -5687,27 +5672,27 @@
         <v>405</v>
       </c>
       <c r="L81" s="6"/>
-      <c r="M81" s="21"/>
-      <c r="N81" s="19"/>
+      <c r="M81" s="19"/>
+      <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="B82" s="14">
+      <c r="B82" s="12">
         <v>3</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="D82" s="14" t="s">
+      <c r="D82" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14" t="s">
+      <c r="F82" s="12"/>
+      <c r="G82" s="12" t="s">
         <v>128</v>
       </c>
       <c r="H82" s="6" t="s">
@@ -5723,27 +5708,27 @@
         <v>405</v>
       </c>
       <c r="L82" s="6"/>
-      <c r="M82" s="21"/>
-      <c r="N82" s="19"/>
+      <c r="M82" s="19"/>
+      <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15" t="s">
+      <c r="A83" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="B83" s="15">
+      <c r="B83" s="13">
         <v>1</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="15" t="s">
+      <c r="E83" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15" t="s">
+      <c r="F83" s="13"/>
+      <c r="G83" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H83" s="10" t="s">
@@ -5758,28 +5743,28 @@
       <c r="K83" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="L83" s="19"/>
-      <c r="M83" s="21"/>
-      <c r="N83" s="19"/>
+      <c r="L83" s="17"/>
+      <c r="M83" s="19"/>
+      <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="B84" s="15">
+      <c r="B84" s="13">
         <v>1</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E84" s="15" t="s">
+      <c r="E84" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15" t="s">
+      <c r="F84" s="13"/>
+      <c r="G84" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H84" s="10" t="s">
@@ -5794,28 +5779,28 @@
       <c r="K84" s="10">
         <v>397</v>
       </c>
-      <c r="L84" s="19"/>
-      <c r="M84" s="21"/>
-      <c r="N84" s="19"/>
+      <c r="L84" s="17"/>
+      <c r="M84" s="19"/>
+      <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="B85" s="15">
+      <c r="B85" s="13">
         <v>1</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E85" s="15" t="s">
+      <c r="E85" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15" t="s">
+      <c r="F85" s="13"/>
+      <c r="G85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H85" s="10" t="s">
@@ -5830,28 +5815,28 @@
       <c r="K85" s="10">
         <v>2048</v>
       </c>
-      <c r="L85" s="19"/>
-      <c r="M85" s="21"/>
-      <c r="N85" s="19"/>
+      <c r="L85" s="17"/>
+      <c r="M85" s="19"/>
+      <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="B86" s="15">
+      <c r="B86" s="13">
         <v>1</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D86" s="15" t="s">
+      <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E86" s="15" t="s">
+      <c r="E86" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15" t="s">
+      <c r="F86" s="13"/>
+      <c r="G86" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H86" s="10" t="s">
@@ -5866,28 +5851,28 @@
       <c r="K86" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="L86" s="19"/>
-      <c r="M86" s="21"/>
-      <c r="N86" s="19"/>
+      <c r="L86" s="17"/>
+      <c r="M86" s="19"/>
+      <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="B87" s="15">
+      <c r="B87" s="13">
         <v>1</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="E87" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15" t="s">
+      <c r="F87" s="13"/>
+      <c r="G87" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H87" s="10" t="s">
@@ -5902,28 +5887,28 @@
       <c r="K87" s="10">
         <v>13123</v>
       </c>
-      <c r="L87" s="19"/>
-      <c r="M87" s="21"/>
-      <c r="N87" s="19"/>
+      <c r="L87" s="17"/>
+      <c r="M87" s="19"/>
+      <c r="N87" s="17"/>
     </row>
     <row r="88" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="B88" s="15">
+      <c r="B88" s="13">
         <v>1</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E88" s="15" t="s">
+      <c r="E88" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15" t="s">
+      <c r="F88" s="13"/>
+      <c r="G88" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="10" t="s">
@@ -5938,28 +5923,28 @@
       <c r="K88" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="L88" s="19"/>
-      <c r="M88" s="21"/>
-      <c r="N88" s="19"/>
+      <c r="L88" s="17"/>
+      <c r="M88" s="19"/>
+      <c r="N88" s="17"/>
     </row>
     <row r="89" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="B89" s="15">
+      <c r="B89" s="13">
         <v>1</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D89" s="15" t="s">
+      <c r="D89" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E89" s="15" t="s">
+      <c r="E89" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15" t="s">
+      <c r="F89" s="13"/>
+      <c r="G89" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H89" s="10" t="s">
@@ -5974,28 +5959,28 @@
       <c r="K89" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="L89" s="19"/>
-      <c r="M89" s="21"/>
-      <c r="N89" s="19"/>
+      <c r="L89" s="17"/>
+      <c r="M89" s="19"/>
+      <c r="N89" s="17"/>
     </row>
     <row r="90" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="15" t="s">
+      <c r="A90" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="B90" s="15">
+      <c r="B90" s="13">
         <v>1</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="15" t="s">
+      <c r="D90" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E90" s="15" t="s">
+      <c r="E90" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15" t="s">
+      <c r="F90" s="13"/>
+      <c r="G90" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H90" s="10" t="s">
@@ -6010,28 +5995,28 @@
       <c r="K90" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="L90" s="19"/>
-      <c r="M90" s="21"/>
-      <c r="N90" s="19"/>
+      <c r="L90" s="17"/>
+      <c r="M90" s="19"/>
+      <c r="N90" s="17"/>
     </row>
     <row r="91" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="B91" s="15">
+      <c r="B91" s="13">
         <v>1</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D91" s="15" t="s">
+      <c r="D91" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E91" s="15" t="s">
+      <c r="E91" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15" t="s">
+      <c r="F91" s="13"/>
+      <c r="G91" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H91" s="10" t="s">
@@ -6046,28 +6031,28 @@
       <c r="K91" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="L91" s="19"/>
-      <c r="M91" s="21"/>
-      <c r="N91" s="21"/>
+      <c r="L91" s="17"/>
+      <c r="M91" s="19"/>
+      <c r="N91" s="19"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="15" t="s">
+      <c r="A92" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="B92" s="15">
+      <c r="B92" s="13">
         <v>1</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D92" s="15" t="s">
+      <c r="D92" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E92" s="15" t="s">
+      <c r="E92" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15" t="s">
+      <c r="F92" s="13"/>
+      <c r="G92" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H92" s="10" t="s">
@@ -6079,31 +6064,31 @@
       <c r="J92" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="K92" s="22" t="s">
+      <c r="K92" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="L92" s="23"/>
-      <c r="M92" s="21"/>
-      <c r="N92" s="21"/>
+      <c r="L92" s="21"/>
+      <c r="M92" s="19"/>
+      <c r="N92" s="19"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="15" t="s">
+      <c r="A93" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="B93" s="15">
+      <c r="B93" s="13">
         <v>1</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E93" s="15" t="s">
+      <c r="E93" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15" t="s">
+      <c r="F93" s="13"/>
+      <c r="G93" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H93" s="10" t="s">
@@ -6115,31 +6100,31 @@
       <c r="J93" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="K93" s="24" t="s">
+      <c r="K93" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="L93" s="23"/>
-      <c r="M93" s="21"/>
-      <c r="N93" s="21"/>
+      <c r="L93" s="21"/>
+      <c r="M93" s="19"/>
+      <c r="N93" s="19"/>
     </row>
     <row r="94" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="15" t="s">
+      <c r="A94" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="B94" s="15">
+      <c r="B94" s="13">
         <v>1</v>
       </c>
-      <c r="C94" s="15" t="s">
+      <c r="C94" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D94" s="15" t="s">
+      <c r="D94" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E94" s="15" t="s">
+      <c r="E94" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15" t="s">
+      <c r="F94" s="13"/>
+      <c r="G94" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H94" s="10" t="s">
@@ -6154,28 +6139,28 @@
       <c r="K94" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="L94" s="19"/>
-      <c r="M94" s="21"/>
-      <c r="N94" s="19"/>
+      <c r="L94" s="17"/>
+      <c r="M94" s="19"/>
+      <c r="N94" s="17"/>
     </row>
     <row r="95" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="B95" s="15">
+      <c r="B95" s="13">
         <v>1</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E95" s="15" t="s">
+      <c r="E95" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15" t="s">
+      <c r="F95" s="13"/>
+      <c r="G95" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H95" s="10" t="s">
@@ -6190,28 +6175,28 @@
       <c r="K95" s="10">
         <v>325</v>
       </c>
-      <c r="L95" s="19"/>
-      <c r="M95" s="21"/>
-      <c r="N95" s="19"/>
+      <c r="L95" s="17"/>
+      <c r="M95" s="19"/>
+      <c r="N95" s="17"/>
     </row>
     <row r="96" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="15" t="s">
+      <c r="A96" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="B96" s="15">
+      <c r="B96" s="13">
         <v>1</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D96" s="15" t="s">
+      <c r="D96" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E96" s="15" t="s">
+      <c r="E96" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15" t="s">
+      <c r="F96" s="13"/>
+      <c r="G96" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H96" s="10" t="s">
@@ -6226,30 +6211,30 @@
       <c r="K96" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="L96" s="19"/>
-      <c r="M96" s="21"/>
-      <c r="N96" s="19"/>
+      <c r="L96" s="17"/>
+      <c r="M96" s="19"/>
+      <c r="N96" s="17"/>
     </row>
     <row r="97" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15" t="s">
+      <c r="A97" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="B97" s="15">
+      <c r="B97" s="13">
         <v>2</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="D97" s="15" t="s">
+      <c r="D97" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E97" s="15" t="s">
+      <c r="E97" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="F97" s="15" t="s">
+      <c r="F97" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="G97" s="15" t="s">
+      <c r="G97" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="10" t="s">
@@ -6264,30 +6249,30 @@
       <c r="K97" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="L97" s="19"/>
-      <c r="M97" s="21"/>
-      <c r="N97" s="19"/>
+      <c r="L97" s="17"/>
+      <c r="M97" s="19"/>
+      <c r="N97" s="17"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="B98" s="15">
+      <c r="B98" s="13">
         <v>2</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="D98" s="15" t="s">
+      <c r="D98" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="F98" s="15" t="s">
+      <c r="F98" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="G98" s="15" t="s">
+      <c r="G98" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H98" s="10" t="s">
@@ -6302,30 +6287,30 @@
       <c r="K98" s="10">
         <v>460</v>
       </c>
-      <c r="L98" s="19"/>
-      <c r="M98" s="21"/>
-      <c r="N98" s="19"/>
+      <c r="L98" s="17"/>
+      <c r="M98" s="19"/>
+      <c r="N98" s="17"/>
     </row>
     <row r="99" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15" t="s">
+      <c r="A99" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="B99" s="15">
+      <c r="B99" s="13">
         <v>2</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="D99" s="15" t="s">
+      <c r="D99" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E99" s="15" t="s">
+      <c r="E99" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="F99" s="15" t="s">
+      <c r="F99" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="G99" s="15" t="s">
+      <c r="G99" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H99" s="10" t="s">
@@ -6340,28 +6325,28 @@
       <c r="K99" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="L99" s="19"/>
-      <c r="M99" s="21"/>
-      <c r="N99" s="19"/>
+      <c r="L99" s="17"/>
+      <c r="M99" s="19"/>
+      <c r="N99" s="17"/>
     </row>
     <row r="100" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="15" t="s">
+      <c r="A100" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="B100" s="15">
+      <c r="B100" s="13">
         <v>3</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="D100" s="15" t="s">
+      <c r="D100" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="E100" s="15" t="s">
+      <c r="E100" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15" t="s">
+      <c r="F100" s="13"/>
+      <c r="G100" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H100" s="10" t="s">
@@ -6376,28 +6361,28 @@
       <c r="K100" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="L100" s="19"/>
-      <c r="M100" s="21"/>
-      <c r="N100" s="19"/>
+      <c r="L100" s="17"/>
+      <c r="M100" s="19"/>
+      <c r="N100" s="17"/>
     </row>
     <row r="101" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15" t="s">
+      <c r="A101" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="B101" s="15">
+      <c r="B101" s="13">
         <v>1</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="D101" s="15" t="s">
+      <c r="D101" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E101" s="15" t="s">
+      <c r="E101" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15" t="s">
+      <c r="F101" s="13"/>
+      <c r="G101" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="10" t="s">
@@ -6412,28 +6397,28 @@
       <c r="K101" s="10">
         <v>58</v>
       </c>
-      <c r="L101" s="19"/>
-      <c r="M101" s="21"/>
-      <c r="N101" s="19"/>
+      <c r="L101" s="17"/>
+      <c r="M101" s="19"/>
+      <c r="N101" s="17"/>
     </row>
     <row r="102" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="15" t="s">
+      <c r="A102" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B102" s="13">
         <v>2</v>
       </c>
-      <c r="C102" s="15" t="s">
+      <c r="C102" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="D102" s="15" t="s">
+      <c r="D102" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E102" s="15" t="s">
+      <c r="E102" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15" t="s">
+      <c r="F102" s="13"/>
+      <c r="G102" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H102" s="10" t="s">
@@ -6448,26 +6433,26 @@
       <c r="K102" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="L102" s="26"/>
-      <c r="M102" s="21"/>
-      <c r="N102" s="19"/>
+      <c r="L102" s="24"/>
+      <c r="M102" s="19"/>
+      <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15" t="s">
+      <c r="A103" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B103" s="13">
         <v>2</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D103" s="15" t="s">
+      <c r="D103" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15" t="s">
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="10" t="s">
@@ -6482,28 +6467,28 @@
       <c r="K103" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="L103" s="26"/>
-      <c r="M103" s="21"/>
-      <c r="N103" s="19"/>
+      <c r="L103" s="24"/>
+      <c r="M103" s="19"/>
+      <c r="N103" s="17"/>
     </row>
     <row r="104" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="15" t="s">
+      <c r="A104" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B104" s="13">
         <v>2</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="D104" s="15" t="s">
+      <c r="D104" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E104" s="15" t="s">
+      <c r="E104" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15" t="s">
+      <c r="F104" s="13"/>
+      <c r="G104" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H104" s="10" t="s">
@@ -6518,28 +6503,28 @@
       <c r="K104" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="L104" s="26"/>
-      <c r="M104" s="21"/>
-      <c r="N104" s="19"/>
+      <c r="L104" s="24"/>
+      <c r="M104" s="19"/>
+      <c r="N104" s="17"/>
     </row>
     <row r="105" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15" t="s">
+      <c r="A105" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B105" s="13">
         <v>2</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D105" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E105" s="15" t="s">
+      <c r="E105" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15" t="s">
+      <c r="F105" s="13"/>
+      <c r="G105" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H105" s="10" t="s">
@@ -6554,28 +6539,28 @@
       <c r="K105" s="10">
         <v>10</v>
       </c>
-      <c r="L105" s="26"/>
-      <c r="M105" s="21"/>
-      <c r="N105" s="19"/>
+      <c r="L105" s="24"/>
+      <c r="M105" s="19"/>
+      <c r="N105" s="17"/>
     </row>
     <row r="106" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="s">
+      <c r="A106" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B106" s="13">
         <v>2</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="D106" s="15" t="s">
+      <c r="D106" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E106" s="15" t="s">
+      <c r="E106" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15" t="s">
+      <c r="F106" s="13"/>
+      <c r="G106" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H106" s="10" t="s">
@@ -6590,28 +6575,28 @@
       <c r="K106" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="L106" s="26"/>
-      <c r="M106" s="21"/>
-      <c r="N106" s="19"/>
+      <c r="L106" s="24"/>
+      <c r="M106" s="19"/>
+      <c r="N106" s="17"/>
     </row>
     <row r="107" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15" t="s">
+      <c r="A107" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B107" s="13">
         <v>1</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="D107" s="15" t="s">
+      <c r="D107" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E107" s="15" t="s">
+      <c r="E107" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15" t="s">
+      <c r="F107" s="13"/>
+      <c r="G107" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H107" s="10" t="s">
@@ -6626,29 +6611,29 @@
       <c r="K107" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="L107" s="26"/>
-      <c r="M107" s="21"/>
-      <c r="N107" s="19"/>
-    </row>
-    <row r="108" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="15" t="s">
+      <c r="L107" s="24"/>
+      <c r="M107" s="19"/>
+      <c r="N107" s="17"/>
+    </row>
+    <row r="108" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B108" s="13">
         <v>1</v>
       </c>
-      <c r="C108" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="D108" s="15" t="s">
+      <c r="C108" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D108" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E108" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15" t="s">
-        <v>128</v>
+      <c r="E108" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>536</v>
@@ -6662,28 +6647,28 @@
       <c r="K108" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="L108" s="26"/>
-      <c r="M108" s="21"/>
-      <c r="N108" s="19"/>
+      <c r="L108" s="24"/>
+      <c r="M108" s="19"/>
+      <c r="N108" s="17"/>
     </row>
     <row r="109" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15" t="s">
+      <c r="A109" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B109" s="13">
         <v>1</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D109" s="15" t="s">
+      <c r="D109" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E109" s="15" t="s">
+      <c r="E109" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15" t="s">
+      <c r="F109" s="13"/>
+      <c r="G109" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H109" s="10" t="s">
@@ -6696,177 +6681,175 @@
         <v>543</v>
       </c>
       <c r="K109" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="L109" s="24"/>
+      <c r="M109" s="19"/>
+      <c r="N109" s="17"/>
+    </row>
+    <row r="110" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="L109" s="26"/>
-      <c r="M109" s="21"/>
-      <c r="N109" s="19"/>
-    </row>
-    <row r="110" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="15" t="s">
+      <c r="B110" s="13">
+        <v>1</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="B110" s="15">
-        <v>1</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E110" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" s="10" t="s">
+      <c r="I110" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="I110" s="10" t="s">
+      <c r="J110" s="10" t="s">
         <v>547</v>
-      </c>
-      <c r="J110" s="10" t="s">
-        <v>548</v>
       </c>
       <c r="K110" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="L110" s="26"/>
-      <c r="M110" s="21"/>
-      <c r="N110" s="19"/>
-    </row>
-    <row r="111" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15" t="s">
+      <c r="L110" s="24"/>
+      <c r="M110" s="19"/>
+      <c r="N110" s="17"/>
+    </row>
+    <row r="111" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B111" s="13">
+        <v>1</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="B111" s="15">
-        <v>1</v>
-      </c>
-      <c r="C111" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D111" s="15" t="s">
+      <c r="I111" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="L111" s="24"/>
+      <c r="M111" s="19"/>
+      <c r="N111" s="17"/>
+    </row>
+    <row r="112" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B112" s="13">
+        <v>2</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="F112" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="J112" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="K112" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="L112" s="25"/>
+    </row>
+    <row r="113" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="B113" s="13">
+        <v>2</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="D113" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E111" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15" t="s">
+      <c r="E113" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="F113" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="G113" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H111" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="I111" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="J111" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="K111" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="L111" s="26"/>
-      <c r="M111" s="21"/>
-      <c r="N111" s="19"/>
-    </row>
-    <row r="112" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="B112" s="15">
-        <v>1</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D112" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E112" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="I112" s="10" t="s">
-        <v>555</v>
-      </c>
-      <c r="J112" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="K112" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="L112" s="26"/>
-      <c r="M112" s="21"/>
-      <c r="N112" s="19"/>
-    </row>
-    <row r="113" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15" t="s">
-        <v>558</v>
-      </c>
-      <c r="B113" s="15">
+      <c r="H113" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="I113" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="J113" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="K113" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="L113" s="25"/>
+    </row>
+    <row r="114" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="B114" s="13">
         <v>2</v>
       </c>
-      <c r="C113" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="D113" s="15" t="s">
+      <c r="C114" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="D114" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E113" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F113" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="G113" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="I113" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="J113" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="K113" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="L113" s="27"/>
-    </row>
-    <row r="114" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="B114" s="15">
-        <v>2</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E114" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F114" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="G114" s="15" t="s">
-        <v>14</v>
+      <c r="E114" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>566</v>
@@ -6880,26 +6863,26 @@
       <c r="K114" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="L114" s="27"/>
-    </row>
-    <row r="115" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="s">
+      <c r="L114" s="25"/>
+    </row>
+    <row r="115" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B115" s="13">
         <v>2</v>
       </c>
-      <c r="C115" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="F115" s="15"/>
-      <c r="G115" s="15" t="s">
+      <c r="C115" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H115" s="10" t="s">
@@ -6914,26 +6897,26 @@
       <c r="K115" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="L115" s="27"/>
-    </row>
-    <row r="116" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="15" t="s">
+      <c r="L115" s="25"/>
+    </row>
+    <row r="116" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B116" s="13">
         <v>2</v>
       </c>
-      <c r="C116" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="D116" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E116" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15" t="s">
+      <c r="C116" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="F116" s="13"/>
+      <c r="G116" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H116" s="10" t="s">
@@ -6948,26 +6931,26 @@
       <c r="K116" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="L116" s="27"/>
-    </row>
-    <row r="117" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15" t="s">
+      <c r="L116" s="25"/>
+    </row>
+    <row r="117" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B117" s="13">
         <v>2</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="D117" s="15" t="s">
+      <c r="D117" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E117" s="15" t="s">
+      <c r="E117" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15" t="s">
+      <c r="F117" s="13"/>
+      <c r="G117" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H117" s="10" t="s">
@@ -6982,26 +6965,26 @@
       <c r="K117" s="10" t="s">
         <v>584</v>
       </c>
-      <c r="L117" s="27"/>
-    </row>
-    <row r="118" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="s">
+      <c r="L117" s="25"/>
+    </row>
+    <row r="118" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B118" s="13">
         <v>2</v>
       </c>
-      <c r="C118" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E118" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="F118" s="15"/>
-      <c r="G118" s="15" t="s">
+      <c r="C118" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H118" s="10" t="s">
@@ -7016,75 +6999,41 @@
       <c r="K118" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="L118" s="27"/>
+      <c r="L118" s="25"/>
     </row>
     <row r="119" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15" t="s">
+      <c r="A119" s="13" t="s">
         <v>590</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B119" s="13">
         <v>2</v>
       </c>
-      <c r="C119" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="F119" s="15"/>
-      <c r="G119" s="15" t="s">
+      <c r="C119" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="L119" s="27"/>
-    </row>
-    <row r="120" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="B120" s="15">
-        <v>2</v>
-      </c>
-      <c r="C120" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E120" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="F120" s="15"/>
-      <c r="G120" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="H120" s="10" t="s">
-        <v>597</v>
-      </c>
-      <c r="I120" s="10" t="s">
-        <v>598</v>
-      </c>
-      <c r="J120" s="10" t="s">
-        <v>599</v>
-      </c>
-      <c r="K120" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="L120" s="27"/>
+      <c r="L119" s="25"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L73" xr:uid="{00000000-0009-0000-0000-000001000000}"/>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -7050,6 +7050,6 @@
     <hyperlink ref="K93" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0967C3E6-BF12-494C-B334-BA58677C23DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0563E85-D919-4C67-AE31-FE06B9355352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="639">
   <si>
     <t>id</t>
   </si>
@@ -1696,9 +1696,6 @@
     <t>هل توجد أقسام في الجامعة تضم أقل من 420 شخصًا مسجلين أو يعملون فيها، وإذا كان الأمر كذلك، فما هي؟</t>
   </si>
   <si>
-    <t>Department14 (376), Department6 (405)</t>
-  </si>
-  <si>
     <t>single_kg3_010</t>
   </si>
   <si>
@@ -1786,9 +1783,6 @@
     <t>بالنسبة لكل قسم في الجامعة، ما هو أقصى عدد من المواد التي يدرّسها مدرّس واحد فيه؟</t>
   </si>
   <si>
-    <t>All 15 departments tied at 4.00 (already confirmed by an actual pipeline run — the FR ranking_kg3_001 run hit this exact template shape and returned this exact result)</t>
-  </si>
-  <si>
     <t>ranking_kg1_002</t>
   </si>
   <si>
@@ -1979,6 +1973,42 @@
   </si>
   <si>
     <t>single_kg1 (81) + single_kg2 (81) + cross_kg (36) + open_kg (18) + Tier 2 (54) + Tier 3 (54) = 324</t>
+  </si>
+  <si>
+    <t>Department14 (409)</t>
+  </si>
+  <si>
+    <t>Department0, 4.00, Department1, 4.00, Department2, 4.00, Department3, 4.00, Department4, 4.00, Department5, 4.00, Department6, 4.00, Department7, 4.00, Department8, 4.00, Department9, 4.00, Department10, 4.00, Department11, 4.00, Department12, 4.00, Department13, 4.00, Department14, 4.00</t>
+  </si>
+  <si>
+    <t>filter_numeric_kg3_004</t>
+  </si>
+  <si>
+    <t>filter_numeric_kg3_005</t>
+  </si>
+  <si>
+    <t>Which departments have more than 550 members?</t>
+  </si>
+  <si>
+    <t>Which departments have between 500 and 570 members?</t>
+  </si>
+  <si>
+    <t>Quels départements comptent plus de 550 membres ?</t>
+  </si>
+  <si>
+    <t>Quels départements comptent entre 500 et 570 membres ?</t>
+  </si>
+  <si>
+    <t>ما هي الأقسام التي يزيد عدد أعضائها عن 550؟</t>
+  </si>
+  <si>
+    <t>ما هي الأقسام التي يتراوح عدد أعضائها بين 500 و570؟</t>
+  </si>
+  <si>
+    <t>Department1, 555, Department11, 569, Department4, 578, Department10, 585, Department5, 589, Department8, 616, Department7, 618, Department13, 658, Department0, 719</t>
+  </si>
+  <si>
+    <t>Department12, 512, Department2, 517, Department1, 555, Department11, 569</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2529,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -2511,32 +2541,32 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2545,7 +2575,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B9" s="2"/>
     </row>
@@ -2554,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2562,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2570,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2578,7 +2608,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2586,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2594,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2602,15 +2632,15 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2618,15 +2648,15 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2635,32 +2665,32 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2669,24 +2699,24 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>
@@ -2699,14 +2729,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="17" customWidth="1"/>
     <col min="2" max="2" width="12" style="17" customWidth="1"/>
     <col min="3" max="3" width="22" style="17" customWidth="1"/>
     <col min="4" max="4" width="12" style="17" customWidth="1"/>
-    <col min="5" max="5" width="16" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21" style="17" customWidth="1"/>
     <col min="6" max="6" width="20" style="17" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" style="17" customWidth="1"/>
     <col min="8" max="9" width="46" style="17" customWidth="1"/>
@@ -6609,7 +6639,7 @@
         <v>533</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>534</v>
+        <v>627</v>
       </c>
       <c r="L107" s="24"/>
       <c r="M107" s="19"/>
@@ -6617,7 +6647,7 @@
     </row>
     <row r="108" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B108" s="13">
         <v>1</v>
@@ -6636,16 +6666,16 @@
         <v>14</v>
       </c>
       <c r="H108" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="I108" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="I108" s="10" t="s">
+      <c r="J108" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="J108" s="10" t="s">
+      <c r="K108" s="10" t="s">
         <v>538</v>
-      </c>
-      <c r="K108" s="10" t="s">
-        <v>539</v>
       </c>
       <c r="L108" s="24"/>
       <c r="M108" s="19"/>
@@ -6653,7 +6683,7 @@
     </row>
     <row r="109" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B109" s="13">
         <v>1</v>
@@ -6672,13 +6702,13 @@
         <v>14</v>
       </c>
       <c r="H109" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="I109" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="I109" s="10" t="s">
+      <c r="J109" s="10" t="s">
         <v>542</v>
-      </c>
-      <c r="J109" s="10" t="s">
-        <v>543</v>
       </c>
       <c r="K109" s="10" t="s">
         <v>400</v>
@@ -6689,7 +6719,7 @@
     </row>
     <row r="110" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B110" s="13">
         <v>1</v>
@@ -6708,13 +6738,13 @@
         <v>14</v>
       </c>
       <c r="H110" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="I110" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="I110" s="10" t="s">
+      <c r="J110" s="10" t="s">
         <v>546</v>
-      </c>
-      <c r="J110" s="10" t="s">
-        <v>547</v>
       </c>
       <c r="K110" s="10" t="s">
         <v>400</v>
@@ -6725,7 +6755,7 @@
     </row>
     <row r="111" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B111" s="13">
         <v>1</v>
@@ -6744,16 +6774,16 @@
         <v>14</v>
       </c>
       <c r="H111" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="I111" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="I111" s="10" t="s">
+      <c r="J111" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="J111" s="10" t="s">
+      <c r="K111" s="10" t="s">
         <v>551</v>
-      </c>
-      <c r="K111" s="10" t="s">
-        <v>552</v>
       </c>
       <c r="L111" s="24"/>
       <c r="M111" s="19"/>
@@ -6761,13 +6791,13 @@
     </row>
     <row r="112" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B112" s="13">
         <v>2</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D112" s="13" t="s">
         <v>13</v>
@@ -6776,34 +6806,34 @@
         <v>214</v>
       </c>
       <c r="F112" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H112" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="G112" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="H112" s="10" t="s">
+      <c r="I112" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="I112" s="10" t="s">
+      <c r="J112" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="J112" s="10" t="s">
+      <c r="K112" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="K112" s="10" t="s">
+      <c r="L112" s="25"/>
+    </row>
+    <row r="113" spans="1:12" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="13" t="s">
         <v>558</v>
-      </c>
-      <c r="L112" s="25"/>
-    </row>
-    <row r="113" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="13" t="s">
-        <v>559</v>
       </c>
       <c r="B113" s="13">
         <v>2</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>105</v>
@@ -6812,28 +6842,28 @@
         <v>214</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H113" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="I113" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="I113" s="10" t="s">
+      <c r="J113" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="J113" s="10" t="s">
-        <v>563</v>
-      </c>
       <c r="K113" s="10" t="s">
-        <v>564</v>
+        <v>628</v>
       </c>
       <c r="L113" s="25"/>
     </row>
     <row r="114" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B114" s="13">
         <v>2</v>
@@ -6852,22 +6882,22 @@
         <v>128</v>
       </c>
       <c r="H114" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="J114" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="I114" s="10" t="s">
+      <c r="K114" s="10" t="s">
         <v>567</v>
-      </c>
-      <c r="J114" s="10" t="s">
-        <v>568</v>
-      </c>
-      <c r="K114" s="10" t="s">
-        <v>569</v>
       </c>
       <c r="L114" s="25"/>
     </row>
     <row r="115" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B115" s="13">
         <v>2</v>
@@ -6886,22 +6916,22 @@
         <v>128</v>
       </c>
       <c r="H115" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="J115" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="I115" s="10" t="s">
+      <c r="K115" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="J115" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>574</v>
       </c>
       <c r="L115" s="25"/>
     </row>
     <row r="116" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B116" s="13">
         <v>2</v>
@@ -6920,22 +6950,22 @@
         <v>128</v>
       </c>
       <c r="H116" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="J116" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="I116" s="10" t="s">
+      <c r="K116" s="10" t="s">
         <v>577</v>
-      </c>
-      <c r="J116" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="K116" s="10" t="s">
-        <v>579</v>
       </c>
       <c r="L116" s="25"/>
     </row>
     <row r="117" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B117" s="13">
         <v>2</v>
@@ -6954,22 +6984,22 @@
         <v>128</v>
       </c>
       <c r="H117" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="J117" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="I117" s="10" t="s">
+      <c r="K117" s="10" t="s">
         <v>582</v>
-      </c>
-      <c r="J117" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="K117" s="10" t="s">
-        <v>584</v>
       </c>
       <c r="L117" s="25"/>
     </row>
     <row r="118" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B118" s="13">
         <v>2</v>
@@ -6988,52 +7018,118 @@
         <v>128</v>
       </c>
       <c r="H118" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="J118" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="I118" s="10" t="s">
+      <c r="K118" s="10" t="s">
         <v>587</v>
-      </c>
-      <c r="J118" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="K118" s="10" t="s">
-        <v>589</v>
       </c>
       <c r="L118" s="25"/>
     </row>
     <row r="119" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B119" s="13">
         <v>2</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>105</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F119" s="13"/>
       <c r="G119" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H119" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="J119" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="I119" s="10" t="s">
+      <c r="K119" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="J119" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="K119" s="10" t="s">
-        <v>595</v>
-      </c>
       <c r="L119" s="25"/>
+    </row>
+    <row r="120" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="B120" s="9">
+        <v>1</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="F120" s="9"/>
+      <c r="G120" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H120" s="21" t="s">
+        <v>631</v>
+      </c>
+      <c r="I120" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="J120" s="21" t="s">
+        <v>635</v>
+      </c>
+      <c r="K120" s="10" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B121" s="9">
+        <v>1</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="F121" s="9"/>
+      <c r="G121" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="I121" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="J121" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="K121" s="10" t="s">
+        <v>638</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L73" xr:uid="{00000000-0009-0000-0000-000001000000}"/>

--- a/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0563E85-D919-4C67-AE31-FE06B9355352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3072D6E3-5721-4D34-A45B-140B0D19B000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1765,9 +1765,6 @@
     <t>من بين جميع شركات الطيران المشغّلة للرحلات في هذه المجموعة من البيانات، أيها تسجل أعلى متوسط سرعة عمودية عبر رحلاتها؟</t>
   </si>
   <si>
-    <t>BEL (3072.0, n=1 flight — see caveat below)</t>
-  </si>
-  <si>
     <t>group_aggregate_kg3_001</t>
   </si>
   <si>
@@ -1795,9 +1792,6 @@
     <t>ما هي الرحلات التي سجّلت أكثر قيم السرعة العمودية سلبية — أي أسرع معدلات الهبوط — في هذه المجموعة من البيانات؟</t>
   </si>
   <si>
-    <t>OS52 and OS214 tied at -2496 (2-way tie), then VF535 at -2432</t>
-  </si>
-  <si>
     <t>ranking_kg3_002</t>
   </si>
   <si>
@@ -1858,9 +1852,6 @@
     <t>AI180 is higher (AI180: 504, PC904: 478)</t>
   </si>
   <si>
-    <t>compare_two_departments_002</t>
-  </si>
-  <si>
     <t>compare_two_departments</t>
   </si>
   <si>
@@ -1978,9 +1969,6 @@
     <t>Department14 (409)</t>
   </si>
   <si>
-    <t>Department0, 4.00, Department1, 4.00, Department2, 4.00, Department3, 4.00, Department4, 4.00, Department5, 4.00, Department6, 4.00, Department7, 4.00, Department8, 4.00, Department9, 4.00, Department10, 4.00, Department11, 4.00, Department12, 4.00, Department13, 4.00, Department14, 4.00</t>
-  </si>
-  <si>
     <t>filter_numeric_kg3_004</t>
   </si>
   <si>
@@ -2005,10 +1993,47 @@
     <t>ما هي الأقسام التي يتراوح عدد أعضائها بين 500 و570؟</t>
   </si>
   <si>
-    <t>Department1, 555, Department11, 569, Department4, 578, Department10, 585, Department5, 589, Department8, 616, Department7, 618, Department13, 658, Department0, 719</t>
-  </si>
-  <si>
-    <t>Department12, 512, Department2, 517, Department1, 555, Department11, 569</t>
+    <t>BEL, 3072.00</t>
+  </si>
+  <si>
+    <t>compare_two_departments_001</t>
+  </si>
+  <si>
+    <t>Department0, 4.00
+ Department1, 4.00
+Department2, 4.00
+Department3, 4.00
+ Department4, 4.00
+Department5, 4.00
+ Department6, 4.00
+ Department7, 4.00
+ Department8, 4.00
+ Department9, 4.00
+ Department10, 4.00
+Department11, 4.00
+Department12, 4.00
+Department13, 4.00
+Department14, 4.00</t>
+  </si>
+  <si>
+    <t>Department1, 555
+ Department11, 569
+ Department4, 578
+ Department10, 585
+Department5, 589
+Department8, 616
+ Department7, 618
+ Department13, 658
+ Department0, 719</t>
+  </si>
+  <si>
+    <t>Department12, 512
+Department2, 517
+ Department1, 555
+ Department11, 569</t>
+  </si>
+  <si>
+    <t>['OS52', 'OS214']</t>
   </si>
 </sst>
 </file>
@@ -2529,7 +2554,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -2541,32 +2566,32 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2575,7 +2600,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B9" s="2"/>
     </row>
@@ -2584,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2592,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2600,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2608,7 +2633,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2616,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2624,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2632,15 +2657,15 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2648,15 +2673,15 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2665,32 +2690,32 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2699,24 +2724,24 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -6639,7 +6664,7 @@
         <v>533</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="L107" s="24"/>
       <c r="M107" s="19"/>
@@ -6821,19 +6846,19 @@
         <v>556</v>
       </c>
       <c r="K112" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="L112" s="25"/>
+    </row>
+    <row r="113" spans="1:12" ht="241.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="13" t="s">
         <v>557</v>
-      </c>
-      <c r="L112" s="25"/>
-    </row>
-    <row r="113" spans="1:12" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="13" t="s">
-        <v>558</v>
       </c>
       <c r="B113" s="13">
         <v>2</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>105</v>
@@ -6842,28 +6867,28 @@
         <v>214</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H113" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="I113" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="I113" s="10" t="s">
+      <c r="J113" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="J113" s="10" t="s">
-        <v>562</v>
-      </c>
       <c r="K113" s="10" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="L113" s="25"/>
     </row>
     <row r="114" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B114" s="13">
         <v>2</v>
@@ -6882,22 +6907,22 @@
         <v>128</v>
       </c>
       <c r="H114" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="I114" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="I114" s="10" t="s">
+      <c r="J114" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="J114" s="10" t="s">
-        <v>566</v>
-      </c>
       <c r="K114" s="10" t="s">
-        <v>567</v>
+        <v>638</v>
       </c>
       <c r="L114" s="25"/>
     </row>
     <row r="115" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B115" s="13">
         <v>2</v>
@@ -6916,22 +6941,22 @@
         <v>128</v>
       </c>
       <c r="H115" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="J115" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="I115" s="10" t="s">
+      <c r="K115" s="10" t="s">
         <v>570</v>
-      </c>
-      <c r="J115" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>572</v>
       </c>
       <c r="L115" s="25"/>
     </row>
     <row r="116" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B116" s="13">
         <v>2</v>
@@ -6950,22 +6975,22 @@
         <v>128</v>
       </c>
       <c r="H116" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="J116" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="I116" s="10" t="s">
+      <c r="K116" s="10" t="s">
         <v>575</v>
-      </c>
-      <c r="J116" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="K116" s="10" t="s">
-        <v>577</v>
       </c>
       <c r="L116" s="25"/>
     </row>
     <row r="117" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B117" s="13">
         <v>2</v>
@@ -6984,22 +7009,22 @@
         <v>128</v>
       </c>
       <c r="H117" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="J117" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="I117" s="10" t="s">
+      <c r="K117" s="10" t="s">
         <v>580</v>
-      </c>
-      <c r="J117" s="10" t="s">
-        <v>581</v>
-      </c>
-      <c r="K117" s="10" t="s">
-        <v>582</v>
       </c>
       <c r="L117" s="25"/>
     </row>
     <row r="118" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B118" s="13">
         <v>2</v>
@@ -7018,56 +7043,56 @@
         <v>128</v>
       </c>
       <c r="H118" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="J118" s="10" t="s">
         <v>584</v>
       </c>
-      <c r="I118" s="10" t="s">
+      <c r="K118" s="10" t="s">
         <v>585</v>
-      </c>
-      <c r="J118" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="K118" s="10" t="s">
-        <v>587</v>
       </c>
       <c r="L118" s="25"/>
     </row>
     <row r="119" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
-        <v>588</v>
+        <v>634</v>
       </c>
       <c r="B119" s="13">
         <v>2</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>105</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F119" s="13"/>
       <c r="G119" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H119" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="J119" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="K119" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="I119" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="J119" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="K119" s="10" t="s">
-        <v>593</v>
-      </c>
       <c r="L119" s="25"/>
     </row>
-    <row r="120" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="158.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B120" s="9">
         <v>1</v>
@@ -7086,21 +7111,21 @@
         <v>128</v>
       </c>
       <c r="H120" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="I120" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="J120" s="21" t="s">
         <v>631</v>
       </c>
-      <c r="I120" s="21" t="s">
-        <v>633</v>
-      </c>
-      <c r="J120" s="21" t="s">
-        <v>635</v>
-      </c>
       <c r="K120" s="10" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B121" s="9">
         <v>1</v>
@@ -7119,16 +7144,16 @@
         <v>128</v>
       </c>
       <c r="H121" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="I121" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="J121" s="21" t="s">
         <v>632</v>
       </c>
-      <c r="I121" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="J121" s="21" t="s">
-        <v>636</v>
-      </c>
       <c r="K121" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
